--- a/research/traditional_assets/database/data/bangladesh/bangladesh_real_estate_development.xlsx
+++ b/research/traditional_assets/database/data/bangladesh/bangladesh_real_estate_development.xlsx
@@ -1278,7 +1278,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1415,22 +1415,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.09783688756789524</v>
+        <v>0.09757487690519155</v>
       </c>
       <c r="C2">
-        <v>52.13555615905649</v>
+        <v>51.82362829392422</v>
       </c>
       <c r="D2">
-        <v>51.13555615905649</v>
+        <v>51.34428829392422</v>
       </c>
       <c r="E2">
-        <v>-0.266</v>
+        <v>0.25466</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>0.52066</v>
       </c>
       <c r="G2">
         <v>1</v>
@@ -1451,28 +1451,28 @@
         <v>4.076000000000001</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.026189198</v>
       </c>
       <c r="N2">
-        <v>4.076000000000001</v>
+        <v>4.049810802000001</v>
       </c>
       <c r="O2">
-        <v>1.2228</v>
+        <v>1.2149432406</v>
       </c>
       <c r="P2">
-        <v>2.8532</v>
+        <v>2.8348675614</v>
       </c>
       <c r="Q2">
-        <v>3.3072</v>
+        <v>3.2888675614</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.09783688756789524</v>
+        <v>0.09820482515675916</v>
       </c>
       <c r="T2">
-        <v>0.4457367247241993</v>
+        <v>0.4488883985353805</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1489,7 +1489,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>155.6366865453459</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1497,22 +1497,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.09757487690519155</v>
+        <v>0.09731286624248787</v>
       </c>
       <c r="C3">
-        <v>51.82362829392422</v>
+        <v>51.51341147616085</v>
       </c>
       <c r="D3">
-        <v>51.34428829392422</v>
+        <v>51.55473147616085</v>
       </c>
       <c r="E3">
-        <v>0.25466</v>
+        <v>0.77532</v>
       </c>
       <c r="F3">
-        <v>0.52066</v>
+        <v>1.04132</v>
       </c>
       <c r="G3">
         <v>1</v>
@@ -1533,28 +1533,28 @@
         <v>4.076000000000001</v>
       </c>
       <c r="M3">
-        <v>0.026189198</v>
+        <v>0.052378396</v>
       </c>
       <c r="N3">
-        <v>4.049810802000001</v>
+        <v>4.023621604000001</v>
       </c>
       <c r="O3">
-        <v>1.2149432406</v>
+        <v>1.2070864812</v>
       </c>
       <c r="P3">
-        <v>2.8348675614</v>
+        <v>2.8165351228</v>
       </c>
       <c r="Q3">
-        <v>3.2888675614</v>
+        <v>3.270535122800001</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.09820482515675916</v>
+        <v>0.09858027167600804</v>
       </c>
       <c r="T3">
-        <v>0.4488883985353805</v>
+        <v>0.4521043922202593</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1571,7 +1571,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>155.6366865453459</v>
+        <v>77.81834327267296</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1579,22 +1579,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.09731286624248787</v>
+        <v>0.09705085557978417</v>
       </c>
       <c r="C4">
-        <v>51.51341147616085</v>
+        <v>51.20492683139772</v>
       </c>
       <c r="D4">
-        <v>51.55473147616085</v>
+        <v>51.76690683139772</v>
       </c>
       <c r="E4">
-        <v>0.77532</v>
+        <v>1.29598</v>
       </c>
       <c r="F4">
-        <v>1.04132</v>
+        <v>1.56198</v>
       </c>
       <c r="G4">
         <v>1</v>
@@ -1615,28 +1615,28 @@
         <v>4.076000000000001</v>
       </c>
       <c r="M4">
-        <v>0.052378396</v>
+        <v>0.07856759399999998</v>
       </c>
       <c r="N4">
-        <v>4.023621604000001</v>
+        <v>3.997432406000001</v>
       </c>
       <c r="O4">
-        <v>1.2070864812</v>
+        <v>1.1992297218</v>
       </c>
       <c r="P4">
-        <v>2.8165351228</v>
+        <v>2.798202684200001</v>
       </c>
       <c r="Q4">
-        <v>3.270535122800001</v>
+        <v>3.252202684200001</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.09858027167600804</v>
+        <v>0.09896345936060225</v>
       </c>
       <c r="T4">
-        <v>0.4521043922202593</v>
+        <v>0.4553866950532798</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1653,7 +1653,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>77.81834327267296</v>
+        <v>51.87889551511532</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1661,22 +1661,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.09705085557978417</v>
+        <v>0.09678884491708051</v>
       </c>
       <c r="C5">
-        <v>51.20492683139772</v>
+        <v>50.89819583447647</v>
       </c>
       <c r="D5">
-        <v>51.76690683139772</v>
+        <v>51.98083583447647</v>
       </c>
       <c r="E5">
-        <v>1.29598</v>
+        <v>1.81664</v>
       </c>
       <c r="F5">
-        <v>1.56198</v>
+        <v>2.08264</v>
       </c>
       <c r="G5">
         <v>1</v>
@@ -1697,28 +1697,28 @@
         <v>4.076000000000001</v>
       </c>
       <c r="M5">
-        <v>0.07856759399999998</v>
+        <v>0.104756792</v>
       </c>
       <c r="N5">
-        <v>3.997432406000001</v>
+        <v>3.971243208000001</v>
       </c>
       <c r="O5">
-        <v>1.1992297218</v>
+        <v>1.1913729624</v>
       </c>
       <c r="P5">
-        <v>2.798202684200001</v>
+        <v>2.779870245600001</v>
       </c>
       <c r="Q5">
-        <v>3.252202684200001</v>
+        <v>3.233870245600001</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.09896345936060225</v>
+        <v>0.09935463012195886</v>
       </c>
       <c r="T5">
-        <v>0.4553866950532798</v>
+        <v>0.4587373791953217</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1735,7 +1735,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>51.87889551511532</v>
+        <v>38.90917163633648</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1743,22 +1743,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.09678884491708051</v>
+        <v>0.09652683425437682</v>
       </c>
       <c r="C6">
-        <v>50.89819583447647</v>
+        <v>50.5932403166948</v>
       </c>
       <c r="D6">
-        <v>51.98083583447647</v>
+        <v>52.19654031669479</v>
       </c>
       <c r="E6">
-        <v>1.81664</v>
+        <v>2.3373</v>
       </c>
       <c r="F6">
-        <v>2.08264</v>
+        <v>2.6033</v>
       </c>
       <c r="G6">
         <v>1</v>
@@ -1779,28 +1779,28 @@
         <v>4.076000000000001</v>
       </c>
       <c r="M6">
-        <v>0.104756792</v>
+        <v>0.13094599</v>
       </c>
       <c r="N6">
-        <v>3.971243208000001</v>
+        <v>3.945054010000001</v>
       </c>
       <c r="O6">
-        <v>1.1913729624</v>
+        <v>1.183516203</v>
       </c>
       <c r="P6">
-        <v>2.779870245600001</v>
+        <v>2.761537807000001</v>
       </c>
       <c r="Q6">
-        <v>3.233870245600001</v>
+        <v>3.215537807000001</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.09935463012195886</v>
+        <v>0.09975403605723876</v>
       </c>
       <c r="T6">
-        <v>0.4587373791953217</v>
+        <v>0.4621586040561434</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1817,7 +1817,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>38.90917163633648</v>
+        <v>31.12733730906919</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1825,22 +1825,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.09652683425437682</v>
+        <v>0.09626482359167313</v>
       </c>
       <c r="C7">
-        <v>50.5932403166948</v>
+        <v>50.29008247323302</v>
       </c>
       <c r="D7">
-        <v>52.19654031669479</v>
+        <v>52.41404247323302</v>
       </c>
       <c r="E7">
-        <v>2.3373</v>
+        <v>2.85796</v>
       </c>
       <c r="F7">
-        <v>2.6033</v>
+        <v>3.12396</v>
       </c>
       <c r="G7">
         <v>1</v>
@@ -1861,28 +1861,28 @@
         <v>4.076000000000001</v>
       </c>
       <c r="M7">
-        <v>0.13094599</v>
+        <v>0.157135188</v>
       </c>
       <c r="N7">
-        <v>3.945054010000001</v>
+        <v>3.918864812000001</v>
       </c>
       <c r="O7">
-        <v>1.183516203</v>
+        <v>1.1756594436</v>
       </c>
       <c r="P7">
-        <v>2.761537807000001</v>
+        <v>2.743205368400001</v>
       </c>
       <c r="Q7">
-        <v>3.215537807000001</v>
+        <v>3.197205368400001</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.09975403605723876</v>
+        <v>0.1001619399911416</v>
       </c>
       <c r="T7">
-        <v>0.4621586040561434</v>
+        <v>0.4656526209352805</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1899,7 +1899,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>31.12733730906919</v>
+        <v>25.93944775755766</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1907,22 +1907,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.09626482359167313</v>
+        <v>0.09600281292896945</v>
       </c>
       <c r="C8">
-        <v>50.29008247323302</v>
+        <v>49.98874487076736</v>
       </c>
       <c r="D8">
-        <v>52.41404247323302</v>
+        <v>52.63336487076736</v>
       </c>
       <c r="E8">
-        <v>2.857959999999999</v>
+        <v>3.378619999999999</v>
       </c>
       <c r="F8">
-        <v>3.123959999999999</v>
+        <v>3.644619999999999</v>
       </c>
       <c r="G8">
         <v>1</v>
@@ -1943,28 +1943,28 @@
         <v>4.076000000000001</v>
       </c>
       <c r="M8">
-        <v>0.157135188</v>
+        <v>0.183324386</v>
       </c>
       <c r="N8">
-        <v>3.918864812000001</v>
+        <v>3.892675614000001</v>
       </c>
       <c r="O8">
-        <v>1.1756594436</v>
+        <v>1.1678026842</v>
       </c>
       <c r="P8">
-        <v>2.743205368400001</v>
+        <v>2.724872929800001</v>
       </c>
       <c r="Q8">
-        <v>3.197205368400001</v>
+        <v>3.178872929800001</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.1001619399911416</v>
+        <v>0.1005786160526553</v>
       </c>
       <c r="T8">
-        <v>0.4656526209352805</v>
+        <v>0.469221777962356</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1981,7 +1981,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>25.93944775755766</v>
+        <v>22.23381236362085</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1989,22 +1989,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.09600281292896944</v>
+        <v>0.09574080226626577</v>
       </c>
       <c r="C9">
-        <v>49.98874487076737</v>
+        <v>49.68925045527502</v>
       </c>
       <c r="D9">
-        <v>52.63336487076737</v>
+        <v>52.85453045527502</v>
       </c>
       <c r="E9">
-        <v>3.37862</v>
+        <v>3.89928</v>
       </c>
       <c r="F9">
-        <v>3.64462</v>
+        <v>4.16528</v>
       </c>
       <c r="G9">
         <v>1</v>
@@ -2025,28 +2025,28 @@
         <v>4.076000000000001</v>
       </c>
       <c r="M9">
-        <v>0.183324386</v>
+        <v>0.209513584</v>
       </c>
       <c r="N9">
-        <v>3.892675614000001</v>
+        <v>3.866486416</v>
       </c>
       <c r="O9">
-        <v>1.1678026842</v>
+        <v>1.1599459248</v>
       </c>
       <c r="P9">
-        <v>2.724872929800001</v>
+        <v>2.7065404912</v>
       </c>
       <c r="Q9">
-        <v>3.178872929800001</v>
+        <v>3.1605404912</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.1005786160526553</v>
+        <v>0.1010043502894193</v>
       </c>
       <c r="T9">
-        <v>0.469221777962356</v>
+        <v>0.4728685253595853</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2063,7 +2063,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>22.23381236362085</v>
+        <v>19.45458581816824</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2071,22 +2071,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.09574080226626577</v>
+        <v>0.09547879160356208</v>
       </c>
       <c r="C10">
-        <v>49.68925045527502</v>
+        <v>49.39162256003701</v>
       </c>
       <c r="D10">
-        <v>52.85453045527502</v>
+        <v>53.07756256003702</v>
       </c>
       <c r="E10">
-        <v>3.89928</v>
+        <v>4.41994</v>
       </c>
       <c r="F10">
-        <v>4.16528</v>
+        <v>4.68594</v>
       </c>
       <c r="G10">
         <v>1</v>
@@ -2107,28 +2107,28 @@
         <v>4.076000000000001</v>
       </c>
       <c r="M10">
-        <v>0.209513584</v>
+        <v>0.235702782</v>
       </c>
       <c r="N10">
-        <v>3.866486416</v>
+        <v>3.840297218</v>
       </c>
       <c r="O10">
-        <v>1.1599459248</v>
+        <v>1.1520891654</v>
       </c>
       <c r="P10">
-        <v>2.7065404912</v>
+        <v>2.6882080526</v>
       </c>
       <c r="Q10">
-        <v>3.1605404912</v>
+        <v>3.1422080526</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.1010043502894193</v>
+        <v>0.1014394413225957</v>
       </c>
       <c r="T10">
-        <v>0.4728685253595853</v>
+        <v>0.4765954210512592</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2145,7 +2145,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>19.45458581816824</v>
+        <v>17.29296517170511</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2153,22 +2153,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.09547879160356208</v>
+        <v>0.09521678094085838</v>
       </c>
       <c r="C11">
-        <v>49.39162256003701</v>
+        <v>49.09588491384432</v>
       </c>
       <c r="D11">
-        <v>53.07756256003702</v>
+        <v>53.30248491384432</v>
       </c>
       <c r="E11">
-        <v>4.41994</v>
+        <v>4.940599999999999</v>
       </c>
       <c r="F11">
-        <v>4.68594</v>
+        <v>5.206599999999999</v>
       </c>
       <c r="G11">
         <v>1</v>
@@ -2189,28 +2189,28 @@
         <v>4.076000000000001</v>
       </c>
       <c r="M11">
-        <v>0.235702782</v>
+        <v>0.2618919799999999</v>
       </c>
       <c r="N11">
-        <v>3.840297218</v>
+        <v>3.814108020000001</v>
       </c>
       <c r="O11">
-        <v>1.1520891654</v>
+        <v>1.144232406</v>
       </c>
       <c r="P11">
-        <v>2.6882080526</v>
+        <v>2.669875614</v>
       </c>
       <c r="Q11">
-        <v>3.1422080526</v>
+        <v>3.123875614000001</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.1014394413225957</v>
+        <v>0.1018842010453982</v>
       </c>
       <c r="T11">
-        <v>0.4765954210512592</v>
+        <v>0.4804051366471925</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2227,7 +2227,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>17.29296517170511</v>
+        <v>15.5636686545346</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2235,22 +2235,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.09521678094085838</v>
+        <v>0.09495477027815472</v>
       </c>
       <c r="C12">
-        <v>49.09588491384432</v>
+        <v>48.80206164941357</v>
       </c>
       <c r="D12">
-        <v>53.30248491384432</v>
+        <v>53.52932164941357</v>
       </c>
       <c r="E12">
-        <v>4.9406</v>
+        <v>5.461259999999999</v>
       </c>
       <c r="F12">
-        <v>5.2066</v>
+        <v>5.727259999999999</v>
       </c>
       <c r="G12">
         <v>1</v>
@@ -2271,28 +2271,28 @@
         <v>4.076000000000001</v>
       </c>
       <c r="M12">
-        <v>0.26189198</v>
+        <v>0.2880811779999999</v>
       </c>
       <c r="N12">
-        <v>3.81410802</v>
+        <v>3.787918822</v>
       </c>
       <c r="O12">
-        <v>1.144232406</v>
+        <v>1.1363756466</v>
       </c>
       <c r="P12">
-        <v>2.669875614</v>
+        <v>2.651543175400001</v>
       </c>
       <c r="Q12">
-        <v>3.123875614000001</v>
+        <v>3.105543175400001</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.1018842010453982</v>
+        <v>0.1023389553687132</v>
       </c>
       <c r="T12">
-        <v>0.4804051366471925</v>
+        <v>0.4843004638295513</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2309,7 +2309,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>15.56366865453459</v>
+        <v>14.14878968594054</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2317,22 +2317,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.09495477027815472</v>
+        <v>0.09469275961545102</v>
       </c>
       <c r="C13">
-        <v>48.80206164941357</v>
+        <v>48.51017731201888</v>
       </c>
       <c r="D13">
-        <v>53.52932164941357</v>
+        <v>53.75809731201888</v>
       </c>
       <c r="E13">
-        <v>5.461259999999999</v>
+        <v>5.981919999999999</v>
       </c>
       <c r="F13">
-        <v>5.727259999999999</v>
+        <v>6.247919999999999</v>
       </c>
       <c r="G13">
         <v>1</v>
@@ -2353,28 +2353,28 @@
         <v>4.076000000000001</v>
       </c>
       <c r="M13">
-        <v>0.2880811779999999</v>
+        <v>0.3142703759999999</v>
       </c>
       <c r="N13">
-        <v>3.787918822</v>
+        <v>3.761729624</v>
       </c>
       <c r="O13">
-        <v>1.1363756466</v>
+        <v>1.1285188872</v>
       </c>
       <c r="P13">
-        <v>2.651543175400001</v>
+        <v>2.633210736800001</v>
       </c>
       <c r="Q13">
-        <v>3.105543175400001</v>
+        <v>3.087210736800001</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.1023389553687132</v>
+        <v>0.102804045017558</v>
       </c>
       <c r="T13">
-        <v>0.4843004638295513</v>
+        <v>0.4882843211751456</v>
       </c>
       <c r="U13">
         <v>0.0503</v>
@@ -2391,7 +2391,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>14.14878968594054</v>
+        <v>12.96972387877883</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2399,22 +2399,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.09469275961545102</v>
+        <v>0.09456724895274733</v>
       </c>
       <c r="C14">
-        <v>48.51017731201888</v>
+        <v>48.09980160597627</v>
       </c>
       <c r="D14">
-        <v>53.75809731201888</v>
+        <v>53.86838160597627</v>
       </c>
       <c r="E14">
-        <v>5.981919999999999</v>
+        <v>6.50258</v>
       </c>
       <c r="F14">
-        <v>6.247919999999999</v>
+        <v>6.76858</v>
       </c>
       <c r="G14">
         <v>1</v>
@@ -2435,45 +2435,45 @@
         <v>4.076000000000001</v>
       </c>
       <c r="M14">
-        <v>0.3142703759999999</v>
+        <v>0.350612444</v>
       </c>
       <c r="N14">
-        <v>3.761729624</v>
+        <v>3.725387556000001</v>
       </c>
       <c r="O14">
-        <v>1.1285188872</v>
+        <v>1.1176162668</v>
       </c>
       <c r="P14">
-        <v>2.633210736800001</v>
+        <v>2.6077712892</v>
       </c>
       <c r="Q14">
-        <v>3.087210736800001</v>
+        <v>3.061771289200001</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.102804045017558</v>
+        <v>0.1032798263824682</v>
       </c>
       <c r="T14">
-        <v>0.4882843211751456</v>
+        <v>0.4923597614482247</v>
       </c>
       <c r="U14">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V14">
         <v>0.3</v>
       </c>
       <c r="W14">
-        <v>0.03521</v>
+        <v>0.03625999999999999</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y14">
-        <v>12.96972387877883</v>
+        <v>11.62537174521963</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2481,22 +2481,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.09456724895274733</v>
+        <v>0.09431573829004364</v>
       </c>
       <c r="C15">
-        <v>48.09980160597627</v>
+        <v>47.80150768671179</v>
       </c>
       <c r="D15">
-        <v>53.86838160597627</v>
+        <v>54.09074768671179</v>
       </c>
       <c r="E15">
-        <v>6.50258</v>
+        <v>7.02324</v>
       </c>
       <c r="F15">
-        <v>6.76858</v>
+        <v>7.28924</v>
       </c>
       <c r="G15">
         <v>1</v>
@@ -2517,28 +2517,28 @@
         <v>4.076000000000001</v>
       </c>
       <c r="M15">
-        <v>0.350612444</v>
+        <v>0.377582632</v>
       </c>
       <c r="N15">
-        <v>3.725387556000001</v>
+        <v>3.698417368</v>
       </c>
       <c r="O15">
-        <v>1.1176162668</v>
+        <v>1.1095252104</v>
       </c>
       <c r="P15">
-        <v>2.6077712892</v>
+        <v>2.5888921576</v>
       </c>
       <c r="Q15">
-        <v>3.061771289200001</v>
+        <v>3.0428921576</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.1032798263824682</v>
+        <v>0.1037666724302833</v>
       </c>
       <c r="T15">
-        <v>0.4923597614482247</v>
+        <v>0.4965299794020731</v>
       </c>
       <c r="U15">
         <v>0.0518</v>
@@ -2555,7 +2555,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>11.62537174521963</v>
+        <v>10.79498804913251</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2563,22 +2563,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.09431573829004364</v>
+        <v>0.09406422762733996</v>
       </c>
       <c r="C16">
-        <v>47.80150768671179</v>
+        <v>47.50505720999854</v>
       </c>
       <c r="D16">
-        <v>54.09074768671179</v>
+        <v>54.31495720999854</v>
       </c>
       <c r="E16">
-        <v>7.02324</v>
+        <v>7.543900000000001</v>
       </c>
       <c r="F16">
-        <v>7.28924</v>
+        <v>7.809900000000001</v>
       </c>
       <c r="G16">
         <v>1</v>
@@ -2599,28 +2599,28 @@
         <v>4.076000000000001</v>
       </c>
       <c r="M16">
-        <v>0.377582632</v>
+        <v>0.40455282</v>
       </c>
       <c r="N16">
-        <v>3.698417368</v>
+        <v>3.67144718</v>
       </c>
       <c r="O16">
-        <v>1.1095252104</v>
+        <v>1.101434154</v>
       </c>
       <c r="P16">
-        <v>2.5888921576</v>
+        <v>2.570013026</v>
       </c>
       <c r="Q16">
-        <v>3.0428921576</v>
+        <v>3.024013026</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.1037666724302833</v>
+        <v>0.1042649736792235</v>
       </c>
       <c r="T16">
-        <v>0.4965299794020731</v>
+        <v>0.5007983201313062</v>
       </c>
       <c r="U16">
         <v>0.0518</v>
@@ -2637,7 +2637,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>10.79498804913251</v>
+        <v>10.07532217919035</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2645,22 +2645,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.09406422762733996</v>
+        <v>0.09400311696463627</v>
       </c>
       <c r="C17">
-        <v>47.50505720999854</v>
+        <v>47.03915535428327</v>
       </c>
       <c r="D17">
-        <v>54.31495720999854</v>
+        <v>54.36971535428327</v>
       </c>
       <c r="E17">
-        <v>7.543899999999999</v>
+        <v>8.06456</v>
       </c>
       <c r="F17">
-        <v>7.809899999999999</v>
+        <v>8.33056</v>
       </c>
       <c r="G17">
         <v>1</v>
@@ -2681,45 +2681,45 @@
         <v>4.076000000000001</v>
       </c>
       <c r="M17">
-        <v>0.4045528199999999</v>
+        <v>0.44568496</v>
       </c>
       <c r="N17">
-        <v>3.67144718</v>
+        <v>3.630315040000001</v>
       </c>
       <c r="O17">
-        <v>1.101434154</v>
+        <v>1.089094512</v>
       </c>
       <c r="P17">
-        <v>2.570013026</v>
+        <v>2.541220528</v>
       </c>
       <c r="Q17">
-        <v>3.024013026</v>
+        <v>2.995220528</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.1042649736792235</v>
+        <v>0.1047751392436146</v>
       </c>
       <c r="T17">
-        <v>0.5007983201313062</v>
+        <v>0.5051682880207592</v>
       </c>
       <c r="U17">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V17">
         <v>0.3</v>
       </c>
       <c r="W17">
-        <v>0.03625999999999999</v>
+        <v>0.03745</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y17">
-        <v>10.07532217919035</v>
+        <v>9.145473520129556</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2727,22 +2727,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.09400311696463627</v>
+        <v>0.09376350630193259</v>
       </c>
       <c r="C18">
-        <v>47.03915535428327</v>
+        <v>46.73426761967379</v>
       </c>
       <c r="D18">
-        <v>54.36971535428327</v>
+        <v>54.58548761967379</v>
       </c>
       <c r="E18">
-        <v>8.06456</v>
+        <v>8.58522</v>
       </c>
       <c r="F18">
-        <v>8.33056</v>
+        <v>8.85122</v>
       </c>
       <c r="G18">
         <v>1</v>
@@ -2763,28 +2763,28 @@
         <v>4.076000000000001</v>
       </c>
       <c r="M18">
-        <v>0.44568496</v>
+        <v>0.47354027</v>
       </c>
       <c r="N18">
-        <v>3.630315040000001</v>
+        <v>3.602459730000001</v>
       </c>
       <c r="O18">
-        <v>1.089094512</v>
+        <v>1.080737919</v>
       </c>
       <c r="P18">
-        <v>2.541220528</v>
+        <v>2.521721811</v>
       </c>
       <c r="Q18">
-        <v>2.995220528</v>
+        <v>2.975721811000001</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.1047751392436146</v>
+        <v>0.1052975979541357</v>
       </c>
       <c r="T18">
-        <v>0.5051682880207592</v>
+        <v>0.5096435563412833</v>
       </c>
       <c r="U18">
         <v>0.0535</v>
@@ -2801,7 +2801,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>9.145473520129556</v>
+        <v>8.607504489533699</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2809,22 +2809,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.09376350630193259</v>
+        <v>0.09352389563922889</v>
       </c>
       <c r="C19">
-        <v>46.73426761967379</v>
+        <v>46.43109934140882</v>
       </c>
       <c r="D19">
-        <v>54.58548761967379</v>
+        <v>54.80297934140882</v>
       </c>
       <c r="E19">
-        <v>8.58522</v>
+        <v>9.105880000000001</v>
       </c>
       <c r="F19">
-        <v>8.85122</v>
+        <v>9.371880000000001</v>
       </c>
       <c r="G19">
         <v>1</v>
@@ -2845,28 +2845,28 @@
         <v>4.076000000000001</v>
       </c>
       <c r="M19">
-        <v>0.47354027</v>
+        <v>0.5013955800000001</v>
       </c>
       <c r="N19">
-        <v>3.602459730000001</v>
+        <v>3.57460442</v>
       </c>
       <c r="O19">
-        <v>1.080737919</v>
+        <v>1.072381326</v>
       </c>
       <c r="P19">
-        <v>2.521721811</v>
+        <v>2.502223094000001</v>
       </c>
       <c r="Q19">
-        <v>2.975721811000001</v>
+        <v>2.956223094000001</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.1052975979541357</v>
+        <v>0.1058327995600352</v>
       </c>
       <c r="T19">
-        <v>0.5096435563412833</v>
+        <v>0.5142279775476738</v>
       </c>
       <c r="U19">
         <v>0.0535</v>
@@ -2883,7 +2883,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>8.607504489533699</v>
+        <v>8.129309795670716</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2891,22 +2891,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.0935238956392289</v>
+        <v>0.0932842849765252</v>
       </c>
       <c r="C20">
-        <v>46.43109934140881</v>
+        <v>46.1296711548372</v>
       </c>
       <c r="D20">
-        <v>54.80297934140881</v>
+        <v>55.02221115483719</v>
       </c>
       <c r="E20">
-        <v>9.105879999999999</v>
+        <v>9.626539999999999</v>
       </c>
       <c r="F20">
-        <v>9.371879999999999</v>
+        <v>9.892539999999999</v>
       </c>
       <c r="G20">
         <v>1</v>
@@ -2927,28 +2927,28 @@
         <v>4.076000000000001</v>
       </c>
       <c r="M20">
-        <v>0.50139558</v>
+        <v>0.5292508899999999</v>
       </c>
       <c r="N20">
-        <v>3.57460442</v>
+        <v>3.54674911</v>
       </c>
       <c r="O20">
-        <v>1.072381326</v>
+        <v>1.064024733</v>
       </c>
       <c r="P20">
-        <v>2.502223094000001</v>
+        <v>2.482724377</v>
       </c>
       <c r="Q20">
-        <v>2.956223094000001</v>
+        <v>2.936724377</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.1058327995600352</v>
+        <v>0.1063812160204015</v>
       </c>
       <c r="T20">
-        <v>0.5142279775476738</v>
+        <v>0.5189255943394072</v>
       </c>
       <c r="U20">
         <v>0.0535</v>
@@ -2965,7 +2965,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>8.129309795670718</v>
+        <v>7.701451385372259</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2973,22 +2973,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.0932842849765252</v>
+        <v>0.09315667431382153</v>
       </c>
       <c r="C21">
-        <v>46.1296711548372</v>
+        <v>45.72648590186283</v>
       </c>
       <c r="D21">
-        <v>55.02221115483719</v>
+        <v>55.13968590186283</v>
       </c>
       <c r="E21">
-        <v>9.626539999999999</v>
+        <v>10.1472</v>
       </c>
       <c r="F21">
-        <v>9.892539999999999</v>
+        <v>10.4132</v>
       </c>
       <c r="G21">
         <v>1</v>
@@ -3009,45 +3009,45 @@
         <v>4.076000000000001</v>
       </c>
       <c r="M21">
-        <v>0.5292508899999999</v>
+        <v>0.56543676</v>
       </c>
       <c r="N21">
-        <v>3.54674911</v>
+        <v>3.510563240000001</v>
       </c>
       <c r="O21">
-        <v>1.064024733</v>
+        <v>1.053168972</v>
       </c>
       <c r="P21">
-        <v>2.482724377</v>
+        <v>2.457394268000001</v>
       </c>
       <c r="Q21">
-        <v>2.936724377</v>
+        <v>2.911394268000001</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.1063812160204015</v>
+        <v>0.1069433428922769</v>
       </c>
       <c r="T21">
-        <v>0.5189255943394072</v>
+        <v>0.5237406515509342</v>
       </c>
       <c r="U21">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V21">
         <v>0.3</v>
       </c>
       <c r="W21">
-        <v>0.03745</v>
+        <v>0.03801</v>
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y21">
-        <v>7.701451385372259</v>
+        <v>7.208586863011879</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3055,22 +3055,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.09315667431382153</v>
+        <v>0.09292266365111787</v>
       </c>
       <c r="C22">
-        <v>45.72648590186283</v>
+        <v>45.42255795313051</v>
       </c>
       <c r="D22">
-        <v>55.13968590186283</v>
+        <v>55.35641795313051</v>
       </c>
       <c r="E22">
-        <v>10.1472</v>
+        <v>10.66786</v>
       </c>
       <c r="F22">
-        <v>10.4132</v>
+        <v>10.93386</v>
       </c>
       <c r="G22">
         <v>1</v>
@@ -3091,28 +3091,28 @@
         <v>4.076000000000001</v>
       </c>
       <c r="M22">
-        <v>0.56543676</v>
+        <v>0.593708598</v>
       </c>
       <c r="N22">
-        <v>3.510563240000001</v>
+        <v>3.482291402</v>
       </c>
       <c r="O22">
-        <v>1.053168972</v>
+        <v>1.0446874206</v>
       </c>
       <c r="P22">
-        <v>2.457394268000001</v>
+        <v>2.437603981400001</v>
       </c>
       <c r="Q22">
-        <v>2.911394268000001</v>
+        <v>2.891603981400001</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.1069433428922769</v>
+        <v>0.1075197008241998</v>
       </c>
       <c r="T22">
-        <v>0.5237406515509342</v>
+        <v>0.5286776089450314</v>
       </c>
       <c r="U22">
         <v>0.0543</v>
@@ -3129,7 +3129,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>7.208586863011879</v>
+        <v>6.865320821916075</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3137,22 +3137,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.09292266365111784</v>
+        <v>0.09268865298841417</v>
       </c>
       <c r="C23">
-        <v>45.42255795313054</v>
+        <v>45.12034050169504</v>
       </c>
       <c r="D23">
-        <v>55.35641795313054</v>
+        <v>55.57486050169503</v>
       </c>
       <c r="E23">
-        <v>10.66786</v>
+        <v>11.18852</v>
       </c>
       <c r="F23">
-        <v>10.93386</v>
+        <v>11.45452</v>
       </c>
       <c r="G23">
         <v>1</v>
@@ -3173,28 +3173,28 @@
         <v>4.076000000000001</v>
       </c>
       <c r="M23">
-        <v>0.593708598</v>
+        <v>0.621980436</v>
       </c>
       <c r="N23">
-        <v>3.482291402</v>
+        <v>3.454019564000001</v>
       </c>
       <c r="O23">
-        <v>1.0446874206</v>
+        <v>1.0362058692</v>
       </c>
       <c r="P23">
-        <v>2.437603981400001</v>
+        <v>2.4178136948</v>
       </c>
       <c r="Q23">
-        <v>2.891603981400001</v>
+        <v>2.871813694800001</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.1075197008241998</v>
+        <v>0.1081108371646335</v>
       </c>
       <c r="T23">
-        <v>0.5286776089450312</v>
+        <v>0.5337411549902591</v>
       </c>
       <c r="U23">
         <v>0.0543</v>
@@ -3211,7 +3211,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>6.865320821916075</v>
+        <v>6.553260784556254</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3219,22 +3219,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.09268865298841417</v>
+        <v>0.09245464232571048</v>
       </c>
       <c r="C24">
-        <v>45.12034050169504</v>
+        <v>44.81985387721404</v>
       </c>
       <c r="D24">
-        <v>55.57486050169503</v>
+        <v>55.79503387721404</v>
       </c>
       <c r="E24">
-        <v>11.18852</v>
+        <v>11.70918</v>
       </c>
       <c r="F24">
-        <v>11.45452</v>
+        <v>11.97518</v>
       </c>
       <c r="G24">
         <v>1</v>
@@ -3255,28 +3255,28 @@
         <v>4.076000000000001</v>
       </c>
       <c r="M24">
-        <v>0.621980436</v>
+        <v>0.650252274</v>
       </c>
       <c r="N24">
-        <v>3.454019564000001</v>
+        <v>3.425747726</v>
       </c>
       <c r="O24">
-        <v>1.0362058692</v>
+        <v>1.0277243178</v>
       </c>
       <c r="P24">
-        <v>2.4178136948</v>
+        <v>2.3980234082</v>
       </c>
       <c r="Q24">
-        <v>2.871813694800001</v>
+        <v>2.8520234082</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.1081108371646335</v>
+        <v>0.1087173276957279</v>
       </c>
       <c r="T24">
-        <v>0.5337411549902591</v>
+        <v>0.5389362217119864</v>
       </c>
       <c r="U24">
         <v>0.0543</v>
@@ -3293,7 +3293,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>6.553260784556254</v>
+        <v>6.268336402619025</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3301,22 +3301,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.09245464232571048</v>
+        <v>0.09238863166300681</v>
       </c>
       <c r="C25">
-        <v>44.81985387721404</v>
+        <v>44.36161707694069</v>
       </c>
       <c r="D25">
-        <v>55.79503387721404</v>
+        <v>55.85745707694069</v>
       </c>
       <c r="E25">
-        <v>11.70918</v>
+        <v>12.22984</v>
       </c>
       <c r="F25">
-        <v>11.97518</v>
+        <v>12.49584</v>
       </c>
       <c r="G25">
         <v>1</v>
@@ -3337,45 +3337,45 @@
         <v>4.076000000000001</v>
       </c>
       <c r="M25">
-        <v>0.650252274</v>
+        <v>0.691019952</v>
       </c>
       <c r="N25">
-        <v>3.425747726</v>
+        <v>3.384980048000001</v>
       </c>
       <c r="O25">
-        <v>1.0277243178</v>
+        <v>1.0154940144</v>
       </c>
       <c r="P25">
-        <v>2.3980234082</v>
+        <v>2.3694860336</v>
       </c>
       <c r="Q25">
-        <v>2.8520234082</v>
+        <v>2.8234860336</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.1087173276957279</v>
+        <v>0.1093397785039563</v>
       </c>
       <c r="T25">
-        <v>0.5389362217119864</v>
+        <v>0.5442680007158645</v>
       </c>
       <c r="U25">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V25">
         <v>0.3</v>
       </c>
       <c r="W25">
-        <v>0.03801</v>
+        <v>0.03871</v>
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y25">
-        <v>6.268336402619025</v>
+        <v>5.898527225158906</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3383,22 +3383,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.09238863166300681</v>
+        <v>0.09216162100030312</v>
       </c>
       <c r="C26">
-        <v>44.36161707694069</v>
+        <v>44.05670071160237</v>
       </c>
       <c r="D26">
-        <v>55.85745707694069</v>
+        <v>56.07320071160238</v>
       </c>
       <c r="E26">
-        <v>12.22984</v>
+        <v>12.7505</v>
       </c>
       <c r="F26">
-        <v>12.49584</v>
+        <v>13.0165</v>
       </c>
       <c r="G26">
         <v>1</v>
@@ -3419,28 +3419,28 @@
         <v>4.076000000000001</v>
       </c>
       <c r="M26">
-        <v>0.6910199519999999</v>
+        <v>0.7198124499999999</v>
       </c>
       <c r="N26">
-        <v>3.384980048000001</v>
+        <v>3.35618755</v>
       </c>
       <c r="O26">
-        <v>1.0154940144</v>
+        <v>1.006856265</v>
       </c>
       <c r="P26">
-        <v>2.3694860336</v>
+        <v>2.349331285</v>
       </c>
       <c r="Q26">
-        <v>2.8234860336</v>
+        <v>2.803331285000001</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.1093397785039563</v>
+        <v>0.1099788280004041</v>
       </c>
       <c r="T26">
-        <v>0.5442680007158645</v>
+        <v>0.5497419604931791</v>
       </c>
       <c r="U26">
         <v>0.0553</v>
@@ -3457,7 +3457,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>5.898527225158907</v>
+        <v>5.66258613615255</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3465,22 +3465,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.09216162100030312</v>
+        <v>0.09193461033759942</v>
       </c>
       <c r="C27">
-        <v>44.05670071160237</v>
+        <v>43.75345738302074</v>
       </c>
       <c r="D27">
-        <v>56.07320071160238</v>
+        <v>56.29061738302074</v>
       </c>
       <c r="E27">
-        <v>12.7505</v>
+        <v>13.27116</v>
       </c>
       <c r="F27">
-        <v>13.0165</v>
+        <v>13.53716</v>
       </c>
       <c r="G27">
         <v>1</v>
@@ -3501,28 +3501,28 @@
         <v>4.076000000000001</v>
       </c>
       <c r="M27">
-        <v>0.7198124499999999</v>
+        <v>0.748604948</v>
       </c>
       <c r="N27">
-        <v>3.35618755</v>
+        <v>3.327395052</v>
       </c>
       <c r="O27">
-        <v>1.006856265</v>
+        <v>0.9982185156000001</v>
       </c>
       <c r="P27">
-        <v>2.349331285</v>
+        <v>2.3291765364</v>
       </c>
       <c r="Q27">
-        <v>2.803331285000001</v>
+        <v>2.783176536400001</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.1099788280004041</v>
+        <v>0.1106351491048641</v>
       </c>
       <c r="T27">
-        <v>0.5497419604931791</v>
+        <v>0.5553638651293401</v>
       </c>
       <c r="U27">
         <v>0.0553</v>
@@ -3539,7 +3539,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>5.66258613615255</v>
+        <v>5.444794361685144</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3547,22 +3547,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.09193461033759942</v>
+        <v>0.09170759967489575</v>
       </c>
       <c r="C28">
-        <v>43.75345738302074</v>
+        <v>43.45190662790566</v>
       </c>
       <c r="D28">
-        <v>56.29061738302074</v>
+        <v>56.50972662790566</v>
       </c>
       <c r="E28">
-        <v>13.27116</v>
+        <v>13.79182</v>
       </c>
       <c r="F28">
-        <v>13.53716</v>
+        <v>14.05782</v>
       </c>
       <c r="G28">
         <v>1</v>
@@ -3583,28 +3583,28 @@
         <v>4.076000000000001</v>
       </c>
       <c r="M28">
-        <v>0.748604948</v>
+        <v>0.777397446</v>
       </c>
       <c r="N28">
-        <v>3.327395052</v>
+        <v>3.298602554</v>
       </c>
       <c r="O28">
-        <v>0.9982185156000001</v>
+        <v>0.9895807662</v>
       </c>
       <c r="P28">
-        <v>2.3291765364</v>
+        <v>2.3090217878</v>
       </c>
       <c r="Q28">
-        <v>2.783176536400001</v>
+        <v>2.763021787800001</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.1106351491048641</v>
+        <v>0.1113094516094462</v>
       </c>
       <c r="T28">
-        <v>0.5553638651293401</v>
+        <v>0.5611397945500537</v>
       </c>
       <c r="U28">
         <v>0.0553</v>
@@ -3621,7 +3621,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>5.444794361685144</v>
+        <v>5.24313531125236</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3629,22 +3629,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.09170759967489575</v>
+        <v>0.09148058901219203</v>
       </c>
       <c r="C29">
-        <v>43.45190662790566</v>
+        <v>43.15206828833958</v>
       </c>
       <c r="D29">
-        <v>56.50972662790566</v>
+        <v>56.73054828833958</v>
       </c>
       <c r="E29">
-        <v>13.79182</v>
+        <v>14.31248</v>
       </c>
       <c r="F29">
-        <v>14.05782</v>
+        <v>14.57848</v>
       </c>
       <c r="G29">
         <v>1</v>
@@ -3665,28 +3665,28 @@
         <v>4.076000000000001</v>
       </c>
       <c r="M29">
-        <v>0.777397446</v>
+        <v>0.8061899440000001</v>
       </c>
       <c r="N29">
-        <v>3.298602554</v>
+        <v>3.269810056</v>
       </c>
       <c r="O29">
-        <v>0.9895807662</v>
+        <v>0.9809430168000001</v>
       </c>
       <c r="P29">
-        <v>2.3090217878</v>
+        <v>2.2888670392</v>
       </c>
       <c r="Q29">
-        <v>2.763021787800001</v>
+        <v>2.742867039200001</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.1113094516094462</v>
+        <v>0.1120024847391556</v>
       </c>
       <c r="T29">
-        <v>0.5611397945500537</v>
+        <v>0.5670761664546757</v>
       </c>
       <c r="U29">
         <v>0.0553</v>
@@ -3703,7 +3703,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>5.24313531125236</v>
+        <v>5.055880478707633</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3711,22 +3711,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.09148058901219203</v>
+        <v>0.09125357834948837</v>
       </c>
       <c r="C30">
-        <v>43.15206828833958</v>
+        <v>42.85396251776708</v>
       </c>
       <c r="D30">
-        <v>56.73054828833958</v>
+        <v>56.95310251776708</v>
       </c>
       <c r="E30">
-        <v>14.31248</v>
+        <v>14.83314</v>
       </c>
       <c r="F30">
-        <v>14.57848</v>
+        <v>15.09914</v>
       </c>
       <c r="G30">
         <v>1</v>
@@ -3747,28 +3747,28 @@
         <v>4.076000000000001</v>
       </c>
       <c r="M30">
-        <v>0.8061899440000001</v>
+        <v>0.834982442</v>
       </c>
       <c r="N30">
-        <v>3.269810056</v>
+        <v>3.241017558</v>
       </c>
       <c r="O30">
-        <v>0.9809430168000001</v>
+        <v>0.9723052674</v>
       </c>
       <c r="P30">
-        <v>2.2888670392</v>
+        <v>2.2687122906</v>
       </c>
       <c r="Q30">
-        <v>2.742867039200001</v>
+        <v>2.722712290600001</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1120024847391556</v>
+        <v>0.1127150399288569</v>
       </c>
       <c r="T30">
-        <v>0.5670761664546757</v>
+        <v>0.5731797601030901</v>
       </c>
       <c r="U30">
         <v>0.0553</v>
@@ -3785,7 +3785,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>5.055880478707633</v>
+        <v>4.881539772545301</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3793,22 +3793,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.09125357834948837</v>
+        <v>0.09102656768678467</v>
       </c>
       <c r="C31">
-        <v>42.85396251776708</v>
+        <v>42.5576097871268</v>
       </c>
       <c r="D31">
-        <v>56.95310251776708</v>
+        <v>57.1774097871268</v>
       </c>
       <c r="E31">
-        <v>14.83314</v>
+        <v>15.3538</v>
       </c>
       <c r="F31">
-        <v>15.09914</v>
+        <v>15.6198</v>
       </c>
       <c r="G31">
         <v>1</v>
@@ -3829,28 +3829,28 @@
         <v>4.076000000000001</v>
       </c>
       <c r="M31">
-        <v>0.8349824419999999</v>
+        <v>0.8637749399999999</v>
       </c>
       <c r="N31">
-        <v>3.241017558000001</v>
+        <v>3.212225060000001</v>
       </c>
       <c r="O31">
-        <v>0.9723052674000001</v>
+        <v>0.9636675180000002</v>
       </c>
       <c r="P31">
-        <v>2.268712290600001</v>
+        <v>2.248557542</v>
       </c>
       <c r="Q31">
-        <v>2.722712290600001</v>
+        <v>2.702557542000001</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1127150399288569</v>
+        <v>0.1134479538382638</v>
       </c>
       <c r="T31">
-        <v>0.5731797601030901</v>
+        <v>0.5794577421414591</v>
       </c>
       <c r="U31">
         <v>0.0553</v>
@@ -3867,7 +3867,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>4.881539772545302</v>
+        <v>4.718821780127126</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3875,22 +3875,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.09102656768678467</v>
+        <v>0.09079955702408098</v>
       </c>
       <c r="C32">
-        <v>42.5576097871268</v>
+        <v>42.26303089112789</v>
       </c>
       <c r="D32">
-        <v>57.1774097871268</v>
+        <v>57.40349089112789</v>
       </c>
       <c r="E32">
-        <v>15.3538</v>
+        <v>15.87446</v>
       </c>
       <c r="F32">
-        <v>15.6198</v>
+        <v>16.14046</v>
       </c>
       <c r="G32">
         <v>1</v>
@@ -3911,28 +3911,28 @@
         <v>4.076000000000001</v>
       </c>
       <c r="M32">
-        <v>0.8637749399999999</v>
+        <v>0.8925674379999999</v>
       </c>
       <c r="N32">
-        <v>3.212225060000001</v>
+        <v>3.183432562000001</v>
       </c>
       <c r="O32">
-        <v>0.9636675180000002</v>
+        <v>0.9550297686000001</v>
       </c>
       <c r="P32">
-        <v>2.248557542</v>
+        <v>2.2284027934</v>
       </c>
       <c r="Q32">
-        <v>2.702557542000001</v>
+        <v>2.682402793400001</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1134479538382638</v>
+        <v>0.1142021116291029</v>
       </c>
       <c r="T32">
-        <v>0.5794577421414591</v>
+        <v>0.5859176946736938</v>
       </c>
       <c r="U32">
         <v>0.0553</v>
@@ -3949,7 +3949,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>4.718821780127126</v>
+        <v>4.56660172270367</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3957,22 +3957,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.09079955702408098</v>
+        <v>0.0911325463613773</v>
       </c>
       <c r="C33">
-        <v>42.26303089112789</v>
+        <v>41.41135369541952</v>
       </c>
       <c r="D33">
-        <v>57.40349089112789</v>
+        <v>57.07247369541953</v>
       </c>
       <c r="E33">
-        <v>15.87446</v>
+        <v>16.39512</v>
       </c>
       <c r="F33">
-        <v>16.14046</v>
+        <v>16.66112</v>
       </c>
       <c r="G33">
         <v>1</v>
@@ -3993,45 +3993,45 @@
         <v>4.076000000000001</v>
       </c>
       <c r="M33">
-        <v>0.8925674379999999</v>
+        <v>0.963012736</v>
       </c>
       <c r="N33">
-        <v>3.183432562000001</v>
+        <v>3.112987264</v>
       </c>
       <c r="O33">
-        <v>0.9550297686000001</v>
+        <v>0.9338961792000001</v>
       </c>
       <c r="P33">
-        <v>2.2284027934</v>
+        <v>2.1790910848</v>
       </c>
       <c r="Q33">
-        <v>2.682402793400001</v>
+        <v>2.633091084800001</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1142021116291029</v>
+        <v>0.1149784505314372</v>
       </c>
       <c r="T33">
-        <v>0.5859176946736938</v>
+        <v>0.5925676458098178</v>
       </c>
       <c r="U33">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V33">
         <v>0.3</v>
       </c>
       <c r="W33">
-        <v>0.03871</v>
+        <v>0.04046</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y33">
-        <v>4.56660172270367</v>
+        <v>4.232550461305634</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4039,22 +4039,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.0911325463613773</v>
+        <v>0.0909230356986736</v>
       </c>
       <c r="C34">
-        <v>41.41135369541952</v>
+        <v>41.09851655308307</v>
       </c>
       <c r="D34">
-        <v>57.07247369541953</v>
+        <v>57.28029655308308</v>
       </c>
       <c r="E34">
-        <v>16.39512</v>
+        <v>16.91578</v>
       </c>
       <c r="F34">
-        <v>16.66112</v>
+        <v>17.18178</v>
       </c>
       <c r="G34">
         <v>1</v>
@@ -4075,28 +4075,28 @@
         <v>4.076000000000001</v>
       </c>
       <c r="M34">
-        <v>0.963012736</v>
+        <v>0.993106884</v>
       </c>
       <c r="N34">
-        <v>3.112987264</v>
+        <v>3.082893116000001</v>
       </c>
       <c r="O34">
-        <v>0.9338961792000001</v>
+        <v>0.9248679348000002</v>
       </c>
       <c r="P34">
-        <v>2.1790910848</v>
+        <v>2.1580251812</v>
       </c>
       <c r="Q34">
-        <v>2.633091084800001</v>
+        <v>2.6120251812</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1149784505314372</v>
+        <v>0.1157779637293636</v>
       </c>
       <c r="T34">
-        <v>0.5925676458098178</v>
+        <v>0.5994161029500054</v>
       </c>
       <c r="U34">
         <v>0.0578</v>
@@ -4113,7 +4113,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>4.232550461305634</v>
+        <v>4.104291356417584</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4121,22 +4121,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.0909230356986736</v>
+        <v>0.09154652503596993</v>
       </c>
       <c r="C35">
-        <v>41.09851655308307</v>
+        <v>39.9637922479379</v>
       </c>
       <c r="D35">
-        <v>57.28029655308308</v>
+        <v>56.66623224793791</v>
       </c>
       <c r="E35">
-        <v>16.91578</v>
+        <v>17.43644</v>
       </c>
       <c r="F35">
-        <v>17.18178</v>
+        <v>17.70244</v>
       </c>
       <c r="G35">
         <v>1</v>
@@ -4157,45 +4157,45 @@
         <v>4.076000000000001</v>
       </c>
       <c r="M35">
-        <v>0.993106884</v>
+        <v>1.085159572</v>
       </c>
       <c r="N35">
-        <v>3.082893116000001</v>
+        <v>2.990840428</v>
       </c>
       <c r="O35">
-        <v>0.9248679348000002</v>
+        <v>0.8972521284</v>
       </c>
       <c r="P35">
-        <v>2.1580251812</v>
+        <v>2.0935882996</v>
       </c>
       <c r="Q35">
-        <v>2.6120251812</v>
+        <v>2.547588299600001</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1157779637293636</v>
+        <v>0.1166017045999544</v>
       </c>
       <c r="T35">
-        <v>0.5994161029500054</v>
+        <v>0.6064720890944408</v>
       </c>
       <c r="U35">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V35">
         <v>0.3</v>
       </c>
       <c r="W35">
-        <v>0.04046</v>
+        <v>0.04291</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y35">
-        <v>4.104291356417584</v>
+        <v>3.756129610033058</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4203,22 +4203,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.09154652503596993</v>
+        <v>0.09136151437326624</v>
       </c>
       <c r="C36">
-        <v>39.9637922479379</v>
+        <v>39.62396804041131</v>
       </c>
       <c r="D36">
-        <v>56.66623224793791</v>
+        <v>56.84706804041132</v>
       </c>
       <c r="E36">
-        <v>17.43644</v>
+        <v>17.9571</v>
       </c>
       <c r="F36">
-        <v>17.70244</v>
+        <v>18.2231</v>
       </c>
       <c r="G36">
         <v>1</v>
@@ -4239,28 +4239,28 @@
         <v>4.076000000000001</v>
       </c>
       <c r="M36">
-        <v>1.085159572</v>
+        <v>1.11707603</v>
       </c>
       <c r="N36">
-        <v>2.990840428</v>
+        <v>2.958923970000001</v>
       </c>
       <c r="O36">
-        <v>0.8972521284</v>
+        <v>0.8876771910000002</v>
       </c>
       <c r="P36">
-        <v>2.0935882996</v>
+        <v>2.071246779</v>
       </c>
       <c r="Q36">
-        <v>2.547588299600001</v>
+        <v>2.525246779000001</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1166017045999544</v>
+        <v>0.1174507913434865</v>
       </c>
       <c r="T36">
-        <v>0.6064720890944408</v>
+        <v>0.613745182504859</v>
       </c>
       <c r="U36">
         <v>0.0613</v>
@@ -4277,7 +4277,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>3.756129610033058</v>
+        <v>3.648811621174971</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4285,22 +4285,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.09136151437326624</v>
+        <v>0.09117650371056255</v>
       </c>
       <c r="C37">
-        <v>39.62396804041131</v>
+        <v>39.28530171035012</v>
       </c>
       <c r="D37">
-        <v>56.84706804041132</v>
+        <v>57.02906171035012</v>
       </c>
       <c r="E37">
-        <v>17.9571</v>
+        <v>18.47776</v>
       </c>
       <c r="F37">
-        <v>18.2231</v>
+        <v>18.74376</v>
       </c>
       <c r="G37">
         <v>1</v>
@@ -4321,28 +4321,28 @@
         <v>4.076000000000001</v>
       </c>
       <c r="M37">
-        <v>1.11707603</v>
+        <v>1.148992488</v>
       </c>
       <c r="N37">
-        <v>2.958923970000001</v>
+        <v>2.927007512</v>
       </c>
       <c r="O37">
-        <v>0.8876771910000002</v>
+        <v>0.8781022536</v>
       </c>
       <c r="P37">
-        <v>2.071246779</v>
+        <v>2.0489052584</v>
       </c>
       <c r="Q37">
-        <v>2.525246779000001</v>
+        <v>2.502905258400001</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1174507913434865</v>
+        <v>0.118326412047754</v>
       </c>
       <c r="T37">
-        <v>0.613745182504859</v>
+        <v>0.6212455600843527</v>
       </c>
       <c r="U37">
         <v>0.0613</v>
@@ -4359,7 +4359,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>3.648811621174971</v>
+        <v>3.547455742808999</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4367,22 +4367,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.09117650371056255</v>
+        <v>0.09171669304785889</v>
       </c>
       <c r="C38">
-        <v>39.28530171035013</v>
+        <v>38.2364969722408</v>
       </c>
       <c r="D38">
-        <v>57.02906171035012</v>
+        <v>56.50091697224079</v>
       </c>
       <c r="E38">
-        <v>18.47776</v>
+        <v>18.99842</v>
       </c>
       <c r="F38">
-        <v>18.74376</v>
+        <v>19.26442</v>
       </c>
       <c r="G38">
         <v>1</v>
@@ -4403,45 +4403,45 @@
         <v>4.076000000000001</v>
       </c>
       <c r="M38">
-        <v>1.148992488</v>
+        <v>1.234849322</v>
       </c>
       <c r="N38">
-        <v>2.927007512</v>
+        <v>2.841150678000001</v>
       </c>
       <c r="O38">
-        <v>0.8781022536</v>
+        <v>0.8523452034000002</v>
       </c>
       <c r="P38">
-        <v>2.0489052584</v>
+        <v>1.988805474600001</v>
       </c>
       <c r="Q38">
-        <v>2.502905258400001</v>
+        <v>2.442805474600001</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.118326412047754</v>
+        <v>0.1192298302346966</v>
       </c>
       <c r="T38">
-        <v>0.6212455600843527</v>
+        <v>0.6289840448885923</v>
       </c>
       <c r="U38">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V38">
         <v>0.3</v>
       </c>
       <c r="W38">
-        <v>0.04291</v>
+        <v>0.04487</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y38">
-        <v>3.547455742808999</v>
+        <v>3.300807578205887</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4449,22 +4449,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.09171669304785889</v>
+        <v>0.09155128238515518</v>
       </c>
       <c r="C39">
-        <v>38.2364969722408</v>
+        <v>37.87651742221968</v>
       </c>
       <c r="D39">
-        <v>56.50091697224079</v>
+        <v>56.66159742221968</v>
       </c>
       <c r="E39">
-        <v>18.99842</v>
+        <v>19.51908</v>
       </c>
       <c r="F39">
-        <v>19.26442</v>
+        <v>19.78508</v>
       </c>
       <c r="G39">
         <v>1</v>
@@ -4485,28 +4485,28 @@
         <v>4.076000000000001</v>
       </c>
       <c r="M39">
-        <v>1.234849322</v>
+        <v>1.268223628</v>
       </c>
       <c r="N39">
-        <v>2.841150678000001</v>
+        <v>2.807776372000001</v>
       </c>
       <c r="O39">
-        <v>0.8523452034000002</v>
+        <v>0.8423329116000001</v>
       </c>
       <c r="P39">
-        <v>1.988805474600001</v>
+        <v>1.9654434604</v>
       </c>
       <c r="Q39">
-        <v>2.442805474600001</v>
+        <v>2.419443460400001</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1192298302346966</v>
+        <v>0.1201623909437987</v>
       </c>
       <c r="T39">
-        <v>0.6289840448885923</v>
+        <v>0.6369721582349042</v>
       </c>
       <c r="U39">
         <v>0.0641</v>
@@ -4523,7 +4523,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>3.300807578205887</v>
+        <v>3.213944220884679</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4531,22 +4531,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.09155128238515518</v>
+        <v>0.09138587172245152</v>
       </c>
       <c r="C40">
-        <v>37.87651742221968</v>
+        <v>37.51745438262159</v>
       </c>
       <c r="D40">
-        <v>56.66159742221968</v>
+        <v>56.82319438262159</v>
       </c>
       <c r="E40">
-        <v>19.51908</v>
+        <v>20.03974</v>
       </c>
       <c r="F40">
-        <v>19.78508</v>
+        <v>20.30574</v>
       </c>
       <c r="G40">
         <v>1</v>
@@ -4567,28 +4567,28 @@
         <v>4.076000000000001</v>
       </c>
       <c r="M40">
-        <v>1.268223628</v>
+        <v>1.301597934</v>
       </c>
       <c r="N40">
-        <v>2.807776372000001</v>
+        <v>2.774402066</v>
       </c>
       <c r="O40">
-        <v>0.8423329116000001</v>
+        <v>0.8323206198</v>
       </c>
       <c r="P40">
-        <v>1.9654434604</v>
+        <v>1.9420814462</v>
       </c>
       <c r="Q40">
-        <v>2.419443460400001</v>
+        <v>2.396081446200001</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1201623909437987</v>
+        <v>0.1211255274138549</v>
       </c>
       <c r="T40">
-        <v>0.6369721582349042</v>
+        <v>0.6452221769368327</v>
       </c>
       <c r="U40">
         <v>0.0641</v>
@@ -4605,7 +4605,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>3.213944220884679</v>
+        <v>3.131535394708148</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4613,22 +4613,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.09138587172245152</v>
+        <v>0.09122046105974783</v>
       </c>
       <c r="C41">
-        <v>37.51745438262159</v>
+        <v>37.15931571744468</v>
       </c>
       <c r="D41">
-        <v>56.82319438262159</v>
+        <v>56.98571571744468</v>
       </c>
       <c r="E41">
-        <v>20.03974</v>
+        <v>20.5604</v>
       </c>
       <c r="F41">
-        <v>20.30574</v>
+        <v>20.8264</v>
       </c>
       <c r="G41">
         <v>1</v>
@@ -4649,28 +4649,28 @@
         <v>4.076000000000001</v>
       </c>
       <c r="M41">
-        <v>1.301597934</v>
+        <v>1.33497224</v>
       </c>
       <c r="N41">
-        <v>2.774402066</v>
+        <v>2.741027760000001</v>
       </c>
       <c r="O41">
-        <v>0.8323206198</v>
+        <v>0.8223083280000002</v>
       </c>
       <c r="P41">
-        <v>1.9420814462</v>
+        <v>1.918719432000001</v>
       </c>
       <c r="Q41">
-        <v>2.396081446200001</v>
+        <v>2.372719432000001</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1211255274138549</v>
+        <v>0.1221207684329131</v>
       </c>
       <c r="T41">
-        <v>0.6452221769368327</v>
+        <v>0.653747196262159</v>
       </c>
       <c r="U41">
         <v>0.0641</v>
@@ -4687,7 +4687,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>3.131535394708148</v>
+        <v>3.053247009840445</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4695,22 +4695,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.09122046105974783</v>
+        <v>0.09329365039704413</v>
       </c>
       <c r="C42">
-        <v>37.15931571744468</v>
+        <v>34.66654932814724</v>
       </c>
       <c r="D42">
-        <v>56.98571571744468</v>
+        <v>55.01360932814724</v>
       </c>
       <c r="E42">
-        <v>20.5604</v>
+        <v>21.08106</v>
       </c>
       <c r="F42">
-        <v>20.8264</v>
+        <v>21.34706</v>
       </c>
       <c r="G42">
         <v>1</v>
@@ -4731,45 +4731,45 @@
         <v>4.076000000000001</v>
       </c>
       <c r="M42">
-        <v>1.33497224</v>
+        <v>1.534853614</v>
       </c>
       <c r="N42">
-        <v>2.741027760000001</v>
+        <v>2.541146386</v>
       </c>
       <c r="O42">
-        <v>0.8223083280000002</v>
+        <v>0.7623439158</v>
       </c>
       <c r="P42">
-        <v>1.918719432000001</v>
+        <v>1.7788024702</v>
       </c>
       <c r="Q42">
-        <v>2.372719432000001</v>
+        <v>2.2328024702</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1221207684329131</v>
+        <v>0.123149746435668</v>
       </c>
       <c r="T42">
-        <v>0.653747196262159</v>
+        <v>0.6625611992934284</v>
       </c>
       <c r="U42">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V42">
         <v>0.3</v>
       </c>
       <c r="W42">
-        <v>0.04487</v>
+        <v>0.05033</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y42">
-        <v>3.053247009840445</v>
+        <v>2.655627848037891</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4777,22 +4777,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.09329365039704413</v>
+        <v>0.09318283973434044</v>
       </c>
       <c r="C43">
-        <v>34.66654932814724</v>
+        <v>34.24783789532011</v>
       </c>
       <c r="D43">
-        <v>55.01360932814724</v>
+        <v>55.11555789532011</v>
       </c>
       <c r="E43">
-        <v>21.08106</v>
+        <v>21.60172</v>
       </c>
       <c r="F43">
-        <v>21.34706</v>
+        <v>21.86772</v>
       </c>
       <c r="G43">
         <v>1</v>
@@ -4813,28 +4813,28 @@
         <v>4.076000000000001</v>
       </c>
       <c r="M43">
-        <v>1.534853614</v>
+        <v>1.572289068</v>
       </c>
       <c r="N43">
-        <v>2.541146386</v>
+        <v>2.503710932000001</v>
       </c>
       <c r="O43">
-        <v>0.7623439158</v>
+        <v>0.7511132796000002</v>
       </c>
       <c r="P43">
-        <v>1.7788024702</v>
+        <v>1.7525976524</v>
       </c>
       <c r="Q43">
-        <v>2.2328024702</v>
+        <v>2.206597652400001</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.123149746435668</v>
+        <v>0.124214206438518</v>
       </c>
       <c r="T43">
-        <v>0.6625611992934284</v>
+        <v>0.6716791334637072</v>
       </c>
       <c r="U43">
         <v>0.07190000000000001</v>
@@ -4851,7 +4851,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>2.655627848037891</v>
+        <v>2.592398613560799</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4859,22 +4859,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.09318283973434044</v>
+        <v>0.09307202907163675</v>
       </c>
       <c r="C44">
-        <v>34.24783789532011</v>
+        <v>33.82950501634492</v>
       </c>
       <c r="D44">
-        <v>55.11555789532011</v>
+        <v>55.21788501634492</v>
       </c>
       <c r="E44">
-        <v>21.60172</v>
+        <v>22.12238</v>
       </c>
       <c r="F44">
-        <v>21.86772</v>
+        <v>22.38838</v>
       </c>
       <c r="G44">
         <v>1</v>
@@ -4895,28 +4895,28 @@
         <v>4.076000000000001</v>
       </c>
       <c r="M44">
-        <v>1.572289068</v>
+        <v>1.609724522</v>
       </c>
       <c r="N44">
-        <v>2.503710932000001</v>
+        <v>2.466275478</v>
       </c>
       <c r="O44">
-        <v>0.7511132796000002</v>
+        <v>0.7398826434000001</v>
       </c>
       <c r="P44">
-        <v>1.7525976524</v>
+        <v>1.7263928346</v>
       </c>
       <c r="Q44">
-        <v>2.206597652400001</v>
+        <v>2.180392834600001</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.124214206438518</v>
+        <v>0.1253160159151522</v>
       </c>
       <c r="T44">
-        <v>0.6716791334637071</v>
+        <v>0.6811169951487326</v>
       </c>
       <c r="U44">
         <v>0.07190000000000001</v>
@@ -4933,7 +4933,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>2.592398613560799</v>
+        <v>2.532110273710548</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4941,22 +4941,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.09307202907163675</v>
+        <v>0.09416241840893308</v>
       </c>
       <c r="C45">
-        <v>33.82950501634492</v>
+        <v>32.31816408338396</v>
       </c>
       <c r="D45">
-        <v>55.21788501634492</v>
+        <v>54.22720408338395</v>
       </c>
       <c r="E45">
-        <v>22.12238</v>
+        <v>22.64304</v>
       </c>
       <c r="F45">
-        <v>22.38838</v>
+        <v>22.90904</v>
       </c>
       <c r="G45">
         <v>1</v>
@@ -4977,45 +4977,45 @@
         <v>4.076000000000001</v>
       </c>
       <c r="M45">
-        <v>1.609724522</v>
+        <v>1.736505232</v>
       </c>
       <c r="N45">
-        <v>2.466275478</v>
+        <v>2.339494768000001</v>
       </c>
       <c r="O45">
-        <v>0.7398826434000001</v>
+        <v>0.7018484304000002</v>
       </c>
       <c r="P45">
-        <v>1.7263928346</v>
+        <v>1.637646337600001</v>
       </c>
       <c r="Q45">
-        <v>2.180392834600001</v>
+        <v>2.091646337600001</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1253160159151522</v>
+        <v>0.1264571757302376</v>
       </c>
       <c r="T45">
-        <v>0.6811169951487326</v>
+        <v>0.6908919233225088</v>
       </c>
       <c r="U45">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V45">
         <v>0.3</v>
       </c>
       <c r="W45">
-        <v>0.05033</v>
+        <v>0.05306</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y45">
-        <v>2.532110273710548</v>
+        <v>2.347243143808737</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5023,22 +5023,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.09416241840893308</v>
+        <v>0.0940789077462294</v>
       </c>
       <c r="C46">
-        <v>32.31816408338396</v>
+        <v>31.87211953167493</v>
       </c>
       <c r="D46">
-        <v>54.22720408338395</v>
+        <v>54.30181953167492</v>
       </c>
       <c r="E46">
-        <v>22.64304</v>
+        <v>23.1637</v>
       </c>
       <c r="F46">
-        <v>22.90904</v>
+        <v>23.4297</v>
       </c>
       <c r="G46">
         <v>1</v>
@@ -5059,28 +5059,28 @@
         <v>4.076000000000001</v>
       </c>
       <c r="M46">
-        <v>1.736505232</v>
+        <v>1.77597126</v>
       </c>
       <c r="N46">
-        <v>2.339494768000001</v>
+        <v>2.300028740000001</v>
       </c>
       <c r="O46">
-        <v>0.7018484304000002</v>
+        <v>0.6900086220000001</v>
       </c>
       <c r="P46">
-        <v>1.637646337600001</v>
+        <v>1.610020118</v>
       </c>
       <c r="Q46">
-        <v>2.091646337600001</v>
+        <v>2.064020118000001</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1264571757302376</v>
+        <v>0.1276398322658716</v>
       </c>
       <c r="T46">
-        <v>0.6908919233225088</v>
+        <v>0.701022303429877</v>
       </c>
       <c r="U46">
         <v>0.07580000000000001</v>
@@ -5097,7 +5097,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>2.347243143808737</v>
+        <v>2.295082185057432</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5105,22 +5105,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.0940789077462294</v>
+        <v>0.09399539708352571</v>
       </c>
       <c r="C47">
-        <v>31.87211953167493</v>
+        <v>31.42628060135036</v>
       </c>
       <c r="D47">
-        <v>54.30181953167492</v>
+        <v>54.37664060135036</v>
       </c>
       <c r="E47">
-        <v>23.1637</v>
+        <v>23.68436</v>
       </c>
       <c r="F47">
-        <v>23.4297</v>
+        <v>23.95036</v>
       </c>
       <c r="G47">
         <v>1</v>
@@ -5141,28 +5141,28 @@
         <v>4.076000000000001</v>
       </c>
       <c r="M47">
-        <v>1.77597126</v>
+        <v>1.815437288</v>
       </c>
       <c r="N47">
-        <v>2.300028740000001</v>
+        <v>2.260562712</v>
       </c>
       <c r="O47">
-        <v>0.6900086220000001</v>
+        <v>0.6781688136000001</v>
       </c>
       <c r="P47">
-        <v>1.610020118</v>
+        <v>1.5823938984</v>
       </c>
       <c r="Q47">
-        <v>2.064020118000001</v>
+        <v>2.036393898400001</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1276398322658716</v>
+        <v>0.128866290895418</v>
       </c>
       <c r="T47">
-        <v>0.701022303429877</v>
+        <v>0.711527882800481</v>
       </c>
       <c r="U47">
         <v>0.07580000000000001</v>
@@ -5179,7 +5179,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>2.295082185057432</v>
+        <v>2.245189094077922</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5187,22 +5187,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.09399539708352571</v>
+        <v>0.09391188642082203</v>
       </c>
       <c r="C48">
-        <v>31.42628060135036</v>
+        <v>30.98064814354413</v>
       </c>
       <c r="D48">
-        <v>54.37664060135036</v>
+        <v>54.45166814354413</v>
       </c>
       <c r="E48">
-        <v>23.68436</v>
+        <v>24.20502</v>
       </c>
       <c r="F48">
-        <v>23.95036</v>
+        <v>24.47102</v>
       </c>
       <c r="G48">
         <v>1</v>
@@ -5223,28 +5223,28 @@
         <v>4.076000000000001</v>
       </c>
       <c r="M48">
-        <v>1.815437288</v>
+        <v>1.854903316</v>
       </c>
       <c r="N48">
-        <v>2.260562712</v>
+        <v>2.221096684</v>
       </c>
       <c r="O48">
-        <v>0.6781688136000001</v>
+        <v>0.6663290052</v>
       </c>
       <c r="P48">
-        <v>1.5823938984</v>
+        <v>1.5547676788</v>
       </c>
       <c r="Q48">
-        <v>2.036393898400001</v>
+        <v>2.0087676788</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.128866290895418</v>
+        <v>0.1301390309826831</v>
       </c>
       <c r="T48">
-        <v>0.711527882800481</v>
+        <v>0.7224298991284663</v>
       </c>
       <c r="U48">
         <v>0.07580000000000001</v>
@@ -5261,7 +5261,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>2.245189094077922</v>
+        <v>2.19741911335286</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5269,22 +5269,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.09391188642082203</v>
+        <v>0.09382837575811834</v>
       </c>
       <c r="C49">
-        <v>30.98064814354413</v>
+        <v>30.53522301409413</v>
       </c>
       <c r="D49">
-        <v>54.45166814354413</v>
+        <v>54.52690301409412</v>
       </c>
       <c r="E49">
-        <v>24.20502</v>
+        <v>24.72568</v>
       </c>
       <c r="F49">
-        <v>24.47102</v>
+        <v>24.99168</v>
       </c>
       <c r="G49">
         <v>1</v>
@@ -5305,28 +5305,28 @@
         <v>4.076000000000001</v>
       </c>
       <c r="M49">
-        <v>1.854903316</v>
+        <v>1.894369344</v>
       </c>
       <c r="N49">
-        <v>2.221096684</v>
+        <v>2.181630656</v>
       </c>
       <c r="O49">
-        <v>0.6663290052</v>
+        <v>0.6544891968000001</v>
       </c>
       <c r="P49">
-        <v>1.5547676788</v>
+        <v>1.5271414592</v>
       </c>
       <c r="Q49">
-        <v>2.0087676788</v>
+        <v>1.9811414592</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1301390309826831</v>
+        <v>0.131460722611766</v>
       </c>
       <c r="T49">
-        <v>0.7224298991284663</v>
+        <v>0.7337512237767588</v>
       </c>
       <c r="U49">
         <v>0.07580000000000001</v>
@@ -5343,7 +5343,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>2.19741911335286</v>
+        <v>2.151639548491342</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5351,22 +5351,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.09382837575811834</v>
+        <v>0.09374486509541465</v>
       </c>
       <c r="C50">
-        <v>30.53522301409413</v>
+        <v>30.09000607357474</v>
       </c>
       <c r="D50">
-        <v>54.52690301409412</v>
+        <v>54.60234607357474</v>
       </c>
       <c r="E50">
-        <v>24.72568</v>
+        <v>25.24634</v>
       </c>
       <c r="F50">
-        <v>24.99168</v>
+        <v>25.51234</v>
       </c>
       <c r="G50">
         <v>1</v>
@@ -5387,28 +5387,28 @@
         <v>4.076000000000001</v>
       </c>
       <c r="M50">
-        <v>1.894369344</v>
+        <v>1.933835372</v>
       </c>
       <c r="N50">
-        <v>2.181630656000001</v>
+        <v>2.142164628000001</v>
       </c>
       <c r="O50">
-        <v>0.6544891968000002</v>
+        <v>0.6426493884000002</v>
       </c>
       <c r="P50">
-        <v>1.527141459200001</v>
+        <v>1.4995152396</v>
       </c>
       <c r="Q50">
-        <v>1.981141459200001</v>
+        <v>1.9535152396</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.131460722611766</v>
+        <v>0.1328342452851267</v>
       </c>
       <c r="T50">
-        <v>0.7337512237767588</v>
+        <v>0.7455165219406705</v>
       </c>
       <c r="U50">
         <v>0.07580000000000001</v>
@@ -5425,7 +5425,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>2.151639548491342</v>
+        <v>2.107728537297642</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5433,22 +5433,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.09374486509541465</v>
+        <v>0.09366135443271095</v>
       </c>
       <c r="C51">
-        <v>30.09000607357474</v>
+        <v>29.64499818732968</v>
       </c>
       <c r="D51">
-        <v>54.60234607357474</v>
+        <v>54.67799818732968</v>
       </c>
       <c r="E51">
-        <v>25.24634</v>
+        <v>25.767</v>
       </c>
       <c r="F51">
-        <v>25.51234</v>
+        <v>26.033</v>
       </c>
       <c r="G51">
         <v>1</v>
@@ -5469,28 +5469,28 @@
         <v>4.076000000000001</v>
       </c>
       <c r="M51">
-        <v>1.933835372</v>
+        <v>1.9733014</v>
       </c>
       <c r="N51">
-        <v>2.142164628000001</v>
+        <v>2.102698600000001</v>
       </c>
       <c r="O51">
-        <v>0.6426493884000002</v>
+        <v>0.6308095800000001</v>
       </c>
       <c r="P51">
-        <v>1.4995152396</v>
+        <v>1.47188902</v>
       </c>
       <c r="Q51">
-        <v>1.9535152396</v>
+        <v>1.92588902</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1328342452851267</v>
+        <v>0.1342627088654219</v>
       </c>
       <c r="T51">
-        <v>0.7455165219406705</v>
+        <v>0.7577524320311387</v>
       </c>
       <c r="U51">
         <v>0.07580000000000001</v>
@@ -5507,7 +5507,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>2.107728537297642</v>
+        <v>2.065573966551689</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5515,22 +5515,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.09366135443271095</v>
+        <v>0.09357784377000727</v>
       </c>
       <c r="C52">
-        <v>29.64499818732968</v>
+        <v>29.20020022550512</v>
       </c>
       <c r="D52">
-        <v>54.67799818732968</v>
+        <v>54.75386022550511</v>
       </c>
       <c r="E52">
-        <v>25.767</v>
+        <v>26.28766</v>
       </c>
       <c r="F52">
-        <v>26.033</v>
+        <v>26.55366</v>
       </c>
       <c r="G52">
         <v>1</v>
@@ -5551,28 +5551,28 @@
         <v>4.076000000000001</v>
       </c>
       <c r="M52">
-        <v>1.9733014</v>
+        <v>2.012767428</v>
       </c>
       <c r="N52">
-        <v>2.102698600000001</v>
+        <v>2.063232572</v>
       </c>
       <c r="O52">
-        <v>0.6308095800000001</v>
+        <v>0.6189697716000001</v>
       </c>
       <c r="P52">
-        <v>1.47188902</v>
+        <v>1.4442628004</v>
       </c>
       <c r="Q52">
-        <v>1.92588902</v>
+        <v>1.8982628004</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1342627088654219</v>
+        <v>0.1357494770816475</v>
       </c>
       <c r="T52">
-        <v>0.7577524320311387</v>
+        <v>0.7704877670232588</v>
       </c>
       <c r="U52">
         <v>0.07580000000000001</v>
@@ -5589,7 +5589,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>2.065573966551689</v>
+        <v>2.025072516227146</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5597,22 +5597,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.09357784377000727</v>
+        <v>0.0986631331073036</v>
       </c>
       <c r="C53">
-        <v>29.20020022550512</v>
+        <v>24.41397721142305</v>
       </c>
       <c r="D53">
-        <v>54.75386022550511</v>
+        <v>50.48829721142305</v>
       </c>
       <c r="E53">
-        <v>26.28766</v>
+        <v>26.80832</v>
       </c>
       <c r="F53">
-        <v>26.55366</v>
+        <v>27.07432</v>
       </c>
       <c r="G53">
         <v>1</v>
@@ -5633,45 +5633,45 @@
         <v>4.076000000000001</v>
       </c>
       <c r="M53">
-        <v>2.012767428</v>
+        <v>2.4366888</v>
       </c>
       <c r="N53">
-        <v>2.063232572</v>
+        <v>1.639311200000001</v>
       </c>
       <c r="O53">
-        <v>0.6189697716000001</v>
+        <v>0.4917933600000002</v>
       </c>
       <c r="P53">
-        <v>1.4442628004</v>
+        <v>1.147517840000001</v>
       </c>
       <c r="Q53">
-        <v>1.8982628004</v>
+        <v>1.601517840000001</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1357494770816475</v>
+        <v>0.1372981939735491</v>
       </c>
       <c r="T53">
-        <v>0.7704877670232588</v>
+        <v>0.7837537409733837</v>
       </c>
       <c r="U53">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V53">
         <v>0.3</v>
       </c>
       <c r="W53">
-        <v>0.05306</v>
+        <v>0.063</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y53">
-        <v>2.025072516227146</v>
+        <v>1.672761823339936</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5679,22 +5679,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.0986631331073036</v>
+        <v>0.0986790224445999</v>
       </c>
       <c r="C54">
-        <v>24.41397721142305</v>
+        <v>23.88103046890856</v>
       </c>
       <c r="D54">
-        <v>50.48829721142305</v>
+        <v>50.47601046890856</v>
       </c>
       <c r="E54">
-        <v>26.80832</v>
+        <v>27.32898</v>
       </c>
       <c r="F54">
-        <v>27.07432</v>
+        <v>27.59498</v>
       </c>
       <c r="G54">
         <v>1</v>
@@ -5715,28 +5715,28 @@
         <v>4.076000000000001</v>
       </c>
       <c r="M54">
-        <v>2.4366888</v>
+        <v>2.4835482</v>
       </c>
       <c r="N54">
-        <v>1.639311200000001</v>
+        <v>1.592451800000001</v>
       </c>
       <c r="O54">
-        <v>0.4917933600000002</v>
+        <v>0.4777355400000001</v>
       </c>
       <c r="P54">
-        <v>1.147517840000001</v>
+        <v>1.11471626</v>
       </c>
       <c r="Q54">
-        <v>1.601517840000001</v>
+        <v>1.56871626</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1372981939735491</v>
+        <v>0.1389128137119147</v>
       </c>
       <c r="T54">
-        <v>0.7837537409733837</v>
+        <v>0.7975842244533012</v>
       </c>
       <c r="U54">
         <v>0.09</v>
@@ -5753,7 +5753,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>1.672761823339936</v>
+        <v>1.641200279503333</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5761,22 +5761,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.0986790224445999</v>
+        <v>0.09869491178189621</v>
       </c>
       <c r="C55">
-        <v>23.88103046890856</v>
+        <v>23.34808970509885</v>
       </c>
       <c r="D55">
-        <v>50.47601046890856</v>
+        <v>50.46372970509885</v>
       </c>
       <c r="E55">
-        <v>27.32898</v>
+        <v>27.84964</v>
       </c>
       <c r="F55">
-        <v>27.59498</v>
+        <v>28.11564</v>
       </c>
       <c r="G55">
         <v>1</v>
@@ -5797,28 +5797,28 @@
         <v>4.076000000000001</v>
       </c>
       <c r="M55">
-        <v>2.4835482</v>
+        <v>2.5304076</v>
       </c>
       <c r="N55">
-        <v>1.592451800000001</v>
+        <v>1.545592400000001</v>
       </c>
       <c r="O55">
-        <v>0.4777355400000001</v>
+        <v>0.4636777200000002</v>
       </c>
       <c r="P55">
-        <v>1.11471626</v>
+        <v>1.081914680000001</v>
       </c>
       <c r="Q55">
-        <v>1.56871626</v>
+        <v>1.535914680000001</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1389128137119147</v>
+        <v>0.14059763430847</v>
       </c>
       <c r="T55">
-        <v>0.7975842244533012</v>
+        <v>0.8120160333019109</v>
       </c>
       <c r="U55">
         <v>0.09</v>
@@ -5835,7 +5835,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>1.641200279503333</v>
+        <v>1.610807681734753</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5843,22 +5843,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.09869491178189621</v>
+        <v>0.09871080111919252</v>
       </c>
       <c r="C56">
-        <v>23.34808970509885</v>
+        <v>22.81515491563115</v>
       </c>
       <c r="D56">
-        <v>50.46372970509885</v>
+        <v>50.45145491563115</v>
       </c>
       <c r="E56">
-        <v>27.84964</v>
+        <v>28.3703</v>
       </c>
       <c r="F56">
-        <v>28.11564</v>
+        <v>28.6363</v>
       </c>
       <c r="G56">
         <v>1</v>
@@ -5879,28 +5879,28 @@
         <v>4.076000000000001</v>
       </c>
       <c r="M56">
-        <v>2.5304076</v>
+        <v>2.577267</v>
       </c>
       <c r="N56">
-        <v>1.545592400000001</v>
+        <v>1.498733000000001</v>
       </c>
       <c r="O56">
-        <v>0.4636777200000002</v>
+        <v>0.4496199000000001</v>
       </c>
       <c r="P56">
-        <v>1.081914680000001</v>
+        <v>1.0491131</v>
       </c>
       <c r="Q56">
-        <v>1.535914680000001</v>
+        <v>1.5031131</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.14059763430847</v>
+        <v>0.1423573358204278</v>
       </c>
       <c r="T56">
-        <v>0.8120160333019109</v>
+        <v>0.8270892558771253</v>
       </c>
       <c r="U56">
         <v>0.09</v>
@@ -5917,7 +5917,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>1.610807681734753</v>
+        <v>1.581520269339576</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5925,22 +5925,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.09871080111919252</v>
+        <v>0.09872669045648885</v>
       </c>
       <c r="C57">
-        <v>22.81515491563115</v>
+        <v>22.28222609614691</v>
       </c>
       <c r="D57">
-        <v>50.45145491563115</v>
+        <v>50.43918609614691</v>
       </c>
       <c r="E57">
-        <v>28.3703</v>
+        <v>28.89096</v>
       </c>
       <c r="F57">
-        <v>28.6363</v>
+        <v>29.15696</v>
       </c>
       <c r="G57">
         <v>1</v>
@@ -5961,28 +5961,28 @@
         <v>4.076000000000001</v>
       </c>
       <c r="M57">
-        <v>2.577267</v>
+        <v>2.6241264</v>
       </c>
       <c r="N57">
-        <v>1.498733000000001</v>
+        <v>1.4518736</v>
       </c>
       <c r="O57">
-        <v>0.4496199000000001</v>
+        <v>0.4355620800000001</v>
       </c>
       <c r="P57">
-        <v>1.0491131</v>
+        <v>1.01631152</v>
       </c>
       <c r="Q57">
-        <v>1.5031131</v>
+        <v>1.47031152</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1423573358204278</v>
+        <v>0.1441970237647474</v>
       </c>
       <c r="T57">
-        <v>0.8270892558771253</v>
+        <v>0.8428476249330314</v>
       </c>
       <c r="U57">
         <v>0.09</v>
@@ -5999,7 +5999,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>1.581520269339576</v>
+        <v>1.553278835958512</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6007,22 +6007,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.09872669045648885</v>
+        <v>0.09874257979378515</v>
       </c>
       <c r="C58">
-        <v>22.28222609614691</v>
+        <v>21.7493032422919</v>
       </c>
       <c r="D58">
-        <v>50.43918609614691</v>
+        <v>50.4269232422919</v>
       </c>
       <c r="E58">
-        <v>28.89096</v>
+        <v>29.41162</v>
       </c>
       <c r="F58">
-        <v>29.15696</v>
+        <v>29.67762</v>
       </c>
       <c r="G58">
         <v>1</v>
@@ -6043,28 +6043,28 @@
         <v>4.076000000000001</v>
       </c>
       <c r="M58">
-        <v>2.6241264</v>
+        <v>2.6709858</v>
       </c>
       <c r="N58">
-        <v>1.4518736</v>
+        <v>1.405014200000001</v>
       </c>
       <c r="O58">
-        <v>0.4355620800000001</v>
+        <v>0.4215042600000001</v>
       </c>
       <c r="P58">
-        <v>1.01631152</v>
+        <v>0.9835099400000005</v>
       </c>
       <c r="Q58">
-        <v>1.47031152</v>
+        <v>1.43750994</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1441970237647474</v>
+        <v>0.1461222785901981</v>
       </c>
       <c r="T58">
-        <v>0.8428476249330314</v>
+        <v>0.8593389413868866</v>
       </c>
       <c r="U58">
         <v>0.09</v>
@@ -6081,7 +6081,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>1.553278835958512</v>
+        <v>1.526028330064503</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6089,22 +6089,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.09874257979378515</v>
+        <v>0.1246062688041476</v>
       </c>
       <c r="C59">
-        <v>21.7493032422919</v>
+        <v>6.930928804596849</v>
       </c>
       <c r="D59">
-        <v>50.4269232422919</v>
+        <v>36.12920880459685</v>
       </c>
       <c r="E59">
-        <v>29.41162</v>
+        <v>29.93228</v>
       </c>
       <c r="F59">
-        <v>29.67762</v>
+        <v>30.19828</v>
       </c>
       <c r="G59">
         <v>1</v>
@@ -6125,45 +6125,45 @@
         <v>4.076000000000001</v>
       </c>
       <c r="M59">
-        <v>2.6709858</v>
+        <v>4.433107504000001</v>
       </c>
       <c r="N59">
-        <v>1.405014200000001</v>
+        <v>-0.357107504</v>
       </c>
       <c r="O59">
-        <v>0.4215042600000001</v>
+        <v>-0.1071322512</v>
       </c>
       <c r="P59">
-        <v>0.9835099400000005</v>
+        <v>-0.2499752528</v>
       </c>
       <c r="Q59">
-        <v>1.43750994</v>
+        <v>0.2040247472</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1461222785901981</v>
+        <v>0.1498758209615245</v>
       </c>
       <c r="T59">
-        <v>0.8593389413868866</v>
+        <v>0.8914909735491787</v>
       </c>
       <c r="U59">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V59">
-        <v>0.3</v>
+        <v>0.2758335995453902</v>
       </c>
       <c r="W59">
-        <v>0.063</v>
+        <v>0.1063076275867367</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y59">
-        <v>1.526028330064503</v>
+        <v>0.9194453318179672</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6171,22 +6171,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.1246062688041476</v>
+        <v>0.1256162688041476</v>
       </c>
       <c r="C60">
-        <v>6.930928804596853</v>
+        <v>6.014618666681102</v>
       </c>
       <c r="D60">
-        <v>36.12920880459685</v>
+        <v>35.7335586666811</v>
       </c>
       <c r="E60">
-        <v>29.93228</v>
+        <v>30.45294</v>
       </c>
       <c r="F60">
-        <v>30.19828</v>
+        <v>30.71894</v>
       </c>
       <c r="G60">
         <v>1</v>
@@ -6207,37 +6207,37 @@
         <v>4.076000000000001</v>
       </c>
       <c r="M60">
-        <v>4.433107504</v>
+        <v>4.509540392</v>
       </c>
       <c r="N60">
-        <v>-0.3571075039999991</v>
+        <v>-0.4335403919999994</v>
       </c>
       <c r="O60">
-        <v>-0.1071322511999997</v>
+        <v>-0.1300621175999998</v>
       </c>
       <c r="P60">
-        <v>-0.2499752527999994</v>
+        <v>-0.3034782743999996</v>
       </c>
       <c r="Q60">
-        <v>0.2040247472000006</v>
+        <v>0.1505217256000004</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1498758209615245</v>
+        <v>0.1524142556191226</v>
       </c>
       <c r="T60">
-        <v>0.8914909735491787</v>
+        <v>0.913234655830866</v>
       </c>
       <c r="U60">
         <v>0.1468</v>
       </c>
       <c r="V60">
-        <v>0.2758335995453902</v>
+        <v>0.2711584537903836</v>
       </c>
       <c r="W60">
-        <v>0.1063076275867367</v>
+        <v>0.1069939389835717</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
@@ -6245,7 +6245,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>0.9194453318179673</v>
+        <v>0.9038615126346119</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6253,22 +6253,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.1256162688041476</v>
+        <v>0.1266262688041476</v>
       </c>
       <c r="C61">
-        <v>6.014618666681102</v>
+        <v>5.10688017208804</v>
       </c>
       <c r="D61">
-        <v>35.7335586666811</v>
+        <v>35.34648017208804</v>
       </c>
       <c r="E61">
-        <v>30.45294</v>
+        <v>30.9736</v>
       </c>
       <c r="F61">
-        <v>30.71894</v>
+        <v>31.2396</v>
       </c>
       <c r="G61">
         <v>1</v>
@@ -6289,37 +6289,37 @@
         <v>4.076000000000001</v>
       </c>
       <c r="M61">
-        <v>4.509540392</v>
+        <v>4.58597328</v>
       </c>
       <c r="N61">
-        <v>-0.4335403919999994</v>
+        <v>-0.5099732799999996</v>
       </c>
       <c r="O61">
-        <v>-0.1300621175999998</v>
+        <v>-0.1529919839999999</v>
       </c>
       <c r="P61">
-        <v>-0.3034782743999996</v>
+        <v>-0.3569812959999997</v>
       </c>
       <c r="Q61">
-        <v>0.1505217256000004</v>
+        <v>0.09701870400000029</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1524142556191226</v>
+        <v>0.1550796120096007</v>
       </c>
       <c r="T61">
-        <v>0.913234655830866</v>
+        <v>0.9360655222266376</v>
       </c>
       <c r="U61">
         <v>0.1468</v>
       </c>
       <c r="V61">
-        <v>0.2711584537903836</v>
+        <v>0.2666391462272105</v>
       </c>
       <c r="W61">
-        <v>0.1069939389835717</v>
+        <v>0.1076573733338455</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
@@ -6327,7 +6327,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>0.9038615126346119</v>
+        <v>0.8887971540907016</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6335,22 +6335,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.1266262688041476</v>
+        <v>0.1276362688041476</v>
       </c>
       <c r="C62">
-        <v>5.10688017208804</v>
+        <v>4.207437752689181</v>
       </c>
       <c r="D62">
-        <v>35.34648017208804</v>
+        <v>34.96769775268918</v>
       </c>
       <c r="E62">
-        <v>30.9736</v>
+        <v>31.49426</v>
       </c>
       <c r="F62">
-        <v>31.2396</v>
+        <v>31.76026</v>
       </c>
       <c r="G62">
         <v>1</v>
@@ -6371,37 +6371,37 @@
         <v>4.076000000000001</v>
       </c>
       <c r="M62">
-        <v>4.58597328</v>
+        <v>4.662406168</v>
       </c>
       <c r="N62">
-        <v>-0.5099732799999996</v>
+        <v>-0.586406167999999</v>
       </c>
       <c r="O62">
-        <v>-0.1529919839999999</v>
+        <v>-0.1759218503999997</v>
       </c>
       <c r="P62">
-        <v>-0.3569812959999997</v>
+        <v>-0.4104843175999993</v>
       </c>
       <c r="Q62">
-        <v>0.09701870400000029</v>
+        <v>0.0435156824000007</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1550796120096007</v>
+        <v>0.1578816533431802</v>
       </c>
       <c r="T62">
-        <v>0.9360655222266376</v>
+        <v>0.9600672022837309</v>
       </c>
       <c r="U62">
         <v>0.1468</v>
       </c>
       <c r="V62">
-        <v>0.2666391462272105</v>
+        <v>0.2622680126825022</v>
       </c>
       <c r="W62">
-        <v>0.1076573733338455</v>
+        <v>0.1082990557382087</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
@@ -6409,7 +6409,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>0.8887971540907016</v>
+        <v>0.8742267089416739</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6417,22 +6417,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.1276362688041476</v>
+        <v>0.1286462688041476</v>
       </c>
       <c r="C63">
-        <v>4.207437752689181</v>
+        <v>3.316027527364653</v>
       </c>
       <c r="D63">
-        <v>34.96769775268918</v>
+        <v>34.59694752736465</v>
       </c>
       <c r="E63">
-        <v>31.49426</v>
+        <v>32.01492</v>
       </c>
       <c r="F63">
-        <v>31.76026</v>
+        <v>32.28091999999999</v>
       </c>
       <c r="G63">
         <v>1</v>
@@ -6453,37 +6453,37 @@
         <v>4.076000000000001</v>
       </c>
       <c r="M63">
-        <v>4.662406168</v>
+        <v>4.738839056</v>
       </c>
       <c r="N63">
-        <v>-0.586406167999999</v>
+        <v>-0.6628390559999993</v>
       </c>
       <c r="O63">
-        <v>-0.1759218503999997</v>
+        <v>-0.1988517167999998</v>
       </c>
       <c r="P63">
-        <v>-0.4104843175999993</v>
+        <v>-0.4639873391999995</v>
       </c>
       <c r="Q63">
-        <v>0.0435156824000007</v>
+        <v>-0.009987339199999445</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1578816533431802</v>
+        <v>0.1608311705364218</v>
       </c>
       <c r="T63">
-        <v>0.9600672022837309</v>
+        <v>0.9853321286596187</v>
       </c>
       <c r="U63">
         <v>0.1468</v>
       </c>
       <c r="V63">
-        <v>0.2622680126825022</v>
+        <v>0.2580378834456876</v>
       </c>
       <c r="W63">
-        <v>0.1082990557382087</v>
+        <v>0.1089200387101731</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
@@ -6491,7 +6491,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>0.8742267089416739</v>
+        <v>0.860126278152292</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6499,22 +6499,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.1286462688041476</v>
+        <v>0.1296562688041476</v>
       </c>
       <c r="C64">
-        <v>3.316027527364653</v>
+        <v>2.432396688937004</v>
       </c>
       <c r="D64">
-        <v>34.59694752736465</v>
+        <v>34.233976688937</v>
       </c>
       <c r="E64">
-        <v>32.01492</v>
+        <v>32.53558</v>
       </c>
       <c r="F64">
-        <v>32.28091999999999</v>
+        <v>32.80157999999999</v>
       </c>
       <c r="G64">
         <v>1</v>
@@ -6535,37 +6535,37 @@
         <v>4.076000000000001</v>
       </c>
       <c r="M64">
-        <v>4.738839056</v>
+        <v>4.815271944</v>
       </c>
       <c r="N64">
-        <v>-0.6628390559999993</v>
+        <v>-0.7392719439999995</v>
       </c>
       <c r="O64">
-        <v>-0.1988517167999998</v>
+        <v>-0.2217815831999999</v>
       </c>
       <c r="P64">
-        <v>-0.4639873391999995</v>
+        <v>-0.5174903607999997</v>
       </c>
       <c r="Q64">
-        <v>-0.009987339199999445</v>
+        <v>-0.06349036079999965</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1608311705364218</v>
+        <v>0.1639401210914602</v>
       </c>
       <c r="T64">
-        <v>0.9853321286596187</v>
+        <v>1.0119627267315</v>
       </c>
       <c r="U64">
         <v>0.1468</v>
       </c>
       <c r="V64">
-        <v>0.2580378834456876</v>
+        <v>0.2539420440259147</v>
       </c>
       <c r="W64">
-        <v>0.1089200387101731</v>
+        <v>0.1095213079369957</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -6573,7 +6573,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>0.860126278152292</v>
+        <v>0.8464734800863826</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6581,22 +6581,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.1296562688041476</v>
+        <v>0.1306662688041476</v>
       </c>
       <c r="C65">
-        <v>2.432396688937004</v>
+        <v>1.556302929295995</v>
       </c>
       <c r="D65">
-        <v>34.233976688937</v>
+        <v>33.878542929296</v>
       </c>
       <c r="E65">
-        <v>32.53558</v>
+        <v>33.05624</v>
       </c>
       <c r="F65">
-        <v>32.80157999999999</v>
+        <v>33.32224</v>
       </c>
       <c r="G65">
         <v>1</v>
@@ -6617,37 +6617,37 @@
         <v>4.076000000000001</v>
       </c>
       <c r="M65">
-        <v>4.815271944</v>
+        <v>4.891704832</v>
       </c>
       <c r="N65">
-        <v>-0.7392719439999995</v>
+        <v>-0.8157048319999998</v>
       </c>
       <c r="O65">
-        <v>-0.2217815831999999</v>
+        <v>-0.2447114495999999</v>
       </c>
       <c r="P65">
-        <v>-0.5174903607999997</v>
+        <v>-0.5709933823999999</v>
       </c>
       <c r="Q65">
-        <v>-0.06349036079999965</v>
+        <v>-0.1169933823999998</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1639401210914602</v>
+        <v>0.1672217911217786</v>
       </c>
       <c r="T65">
-        <v>1.0119627267315</v>
+        <v>1.040072802474042</v>
       </c>
       <c r="U65">
         <v>0.1468</v>
       </c>
       <c r="V65">
-        <v>0.2539420440259147</v>
+        <v>0.2499741995880098</v>
       </c>
       <c r="W65">
-        <v>0.1095213079369957</v>
+        <v>0.1101037875004802</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -6655,7 +6655,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>0.8464734800863826</v>
+        <v>0.8332473319600328</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6663,22 +6663,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.1306662688041476</v>
+        <v>0.1316762688041476</v>
       </c>
       <c r="C66">
-        <v>1.556302929295995</v>
+        <v>0.6875138999672004</v>
       </c>
       <c r="D66">
-        <v>33.878542929296</v>
+        <v>33.5304138999672</v>
       </c>
       <c r="E66">
-        <v>33.05624</v>
+        <v>33.5769</v>
       </c>
       <c r="F66">
-        <v>33.32224</v>
+        <v>33.8429</v>
       </c>
       <c r="G66">
         <v>1</v>
@@ -6699,37 +6699,37 @@
         <v>4.076000000000001</v>
       </c>
       <c r="M66">
-        <v>4.891704832</v>
+        <v>4.968137720000001</v>
       </c>
       <c r="N66">
-        <v>-0.8157048319999998</v>
+        <v>-0.89213772</v>
       </c>
       <c r="O66">
-        <v>-0.2447114495999999</v>
+        <v>-0.267641316</v>
       </c>
       <c r="P66">
-        <v>-0.5709933823999999</v>
+        <v>-0.6244964040000001</v>
       </c>
       <c r="Q66">
-        <v>-0.1169933823999998</v>
+        <v>-0.170496404</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1672217911217786</v>
+        <v>0.1706909851538294</v>
       </c>
       <c r="T66">
-        <v>1.040072802474042</v>
+        <v>1.069789168259015</v>
       </c>
       <c r="U66">
         <v>0.1468</v>
       </c>
       <c r="V66">
-        <v>0.2499741995880098</v>
+        <v>0.2461284426712712</v>
       </c>
       <c r="W66">
-        <v>0.1101037875004802</v>
+        <v>0.1106683446158574</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
@@ -6737,7 +6737,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>0.8332473319600328</v>
+        <v>0.8204281422375707</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6745,22 +6745,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.1316762688041476</v>
+        <v>0.1326862688041476</v>
       </c>
       <c r="C67">
-        <v>0.6875138999672004</v>
+        <v>-0.1741932943992097</v>
       </c>
       <c r="D67">
-        <v>33.5304138999672</v>
+        <v>33.18936670560079</v>
       </c>
       <c r="E67">
-        <v>33.5769</v>
+        <v>34.09756</v>
       </c>
       <c r="F67">
-        <v>33.8429</v>
+        <v>34.36356</v>
       </c>
       <c r="G67">
         <v>1</v>
@@ -6781,37 +6781,37 @@
         <v>4.076000000000001</v>
       </c>
       <c r="M67">
-        <v>4.968137720000001</v>
+        <v>5.044570608000001</v>
       </c>
       <c r="N67">
-        <v>-0.89213772</v>
+        <v>-0.9685706080000003</v>
       </c>
       <c r="O67">
-        <v>-0.267641316</v>
+        <v>-0.2905711824000001</v>
       </c>
       <c r="P67">
-        <v>-0.6244964040000001</v>
+        <v>-0.6779994256000001</v>
       </c>
       <c r="Q67">
-        <v>-0.170496404</v>
+        <v>-0.2239994256000001</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1706909851538294</v>
+        <v>0.1743642494230597</v>
       </c>
       <c r="T67">
-        <v>1.069789168259015</v>
+        <v>1.101253555560751</v>
       </c>
       <c r="U67">
         <v>0.1468</v>
       </c>
       <c r="V67">
-        <v>0.2461284426712712</v>
+        <v>0.2423992238429186</v>
       </c>
       <c r="W67">
-        <v>0.1106683446158574</v>
+        <v>0.1112157939398596</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -6819,7 +6819,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>0.8204281422375707</v>
+        <v>0.8079974128097287</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6827,22 +6827,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.1326862688041476</v>
+        <v>0.1721150751251584</v>
       </c>
       <c r="C68">
-        <v>-0.1741932943992097</v>
+        <v>-10.12782232964406</v>
       </c>
       <c r="D68">
-        <v>33.18936670560079</v>
+        <v>23.75639767035594</v>
       </c>
       <c r="E68">
-        <v>34.09756</v>
+        <v>34.61822</v>
       </c>
       <c r="F68">
-        <v>34.36356</v>
+        <v>34.88422</v>
       </c>
       <c r="G68">
         <v>1</v>
@@ -6863,45 +6863,45 @@
         <v>4.076000000000001</v>
       </c>
       <c r="M68">
-        <v>5.044570608000001</v>
+        <v>7.004751376</v>
       </c>
       <c r="N68">
-        <v>-0.9685706080000003</v>
+        <v>-2.928751375999999</v>
       </c>
       <c r="O68">
-        <v>-0.2905711824000001</v>
+        <v>-0.8786254127999997</v>
       </c>
       <c r="P68">
-        <v>-0.6779994256000001</v>
+        <v>-2.050125963199999</v>
       </c>
       <c r="Q68">
-        <v>-0.2239994256000001</v>
+        <v>-1.596125963199999</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1743642494230597</v>
+        <v>0.1850443973480336</v>
       </c>
       <c r="T68">
-        <v>1.101253555560751</v>
+        <v>1.192737392856678</v>
       </c>
       <c r="U68">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="V68">
-        <v>0.2423992238429186</v>
+        <v>0.1745672236404583</v>
       </c>
       <c r="W68">
-        <v>0.1112157939398596</v>
+        <v>0.165746901492996</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y68">
-        <v>0.8079974128097287</v>
+        <v>0.5818907454681944</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6909,22 +6909,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.1721150751251584</v>
+        <v>0.1736650751251584</v>
       </c>
       <c r="C69">
-        <v>-10.12782232964406</v>
+        <v>-10.91097831108544</v>
       </c>
       <c r="D69">
-        <v>23.75639767035594</v>
+        <v>23.49390168891456</v>
       </c>
       <c r="E69">
-        <v>34.61822</v>
+        <v>35.13888</v>
       </c>
       <c r="F69">
-        <v>34.88422</v>
+        <v>35.40488</v>
       </c>
       <c r="G69">
         <v>1</v>
@@ -6945,37 +6945,37 @@
         <v>4.076000000000001</v>
       </c>
       <c r="M69">
-        <v>7.004751376</v>
+        <v>7.109299904</v>
       </c>
       <c r="N69">
-        <v>-2.928751375999999</v>
+        <v>-3.033299904</v>
       </c>
       <c r="O69">
-        <v>-0.8786254127999997</v>
+        <v>-0.9099899711999999</v>
       </c>
       <c r="P69">
-        <v>-2.050125963199999</v>
+        <v>-2.1233099328</v>
       </c>
       <c r="Q69">
-        <v>-1.596125963199999</v>
+        <v>-1.6693099328</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1850443973480336</v>
+        <v>0.1893957847651597</v>
       </c>
       <c r="T69">
-        <v>1.192737392856678</v>
+        <v>1.23001043638345</v>
       </c>
       <c r="U69">
         <v>0.2008</v>
       </c>
       <c r="V69">
-        <v>0.1745672236404583</v>
+        <v>0.1720000585869222</v>
       </c>
       <c r="W69">
-        <v>0.165746901492996</v>
+        <v>0.166262388235746</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -6983,7 +6983,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.5818907454681944</v>
+        <v>0.5733335286230739</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6991,22 +6991,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.1736650751251584</v>
+        <v>0.1752150751251584</v>
       </c>
       <c r="C70">
-        <v>-10.91097831108544</v>
+        <v>-11.68839679759704</v>
       </c>
       <c r="D70">
-        <v>23.49390168891456</v>
+        <v>23.23714320240295</v>
       </c>
       <c r="E70">
-        <v>35.13888</v>
+        <v>35.65954</v>
       </c>
       <c r="F70">
-        <v>35.40488</v>
+        <v>35.92554</v>
       </c>
       <c r="G70">
         <v>1</v>
@@ -7027,37 +7027,37 @@
         <v>4.076000000000001</v>
       </c>
       <c r="M70">
-        <v>7.109299904</v>
+        <v>7.213848432</v>
       </c>
       <c r="N70">
-        <v>-3.033299904</v>
+        <v>-3.137848431999999</v>
       </c>
       <c r="O70">
-        <v>-0.9099899711999999</v>
+        <v>-0.9413545295999998</v>
       </c>
       <c r="P70">
-        <v>-2.1233099328</v>
+        <v>-2.196493902399999</v>
       </c>
       <c r="Q70">
-        <v>-1.6693099328</v>
+        <v>-1.742493902399999</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.1893957847651597</v>
+        <v>0.1940279068543584</v>
       </c>
       <c r="T70">
-        <v>1.23001043638345</v>
+        <v>1.269688192395819</v>
       </c>
       <c r="U70">
         <v>0.2008</v>
       </c>
       <c r="V70">
-        <v>0.1720000585869222</v>
+        <v>0.1695073041146479</v>
       </c>
       <c r="W70">
-        <v>0.166262388235746</v>
+        <v>0.1667629333337787</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7065,7 +7065,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.5733335286230739</v>
+        <v>0.5650243470488265</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7073,22 +7073,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.1752150751251584</v>
+        <v>0.1767650751251584</v>
       </c>
       <c r="C71">
-        <v>-11.68839679759704</v>
+        <v>-12.4602638661768</v>
       </c>
       <c r="D71">
-        <v>23.23714320240295</v>
+        <v>22.9859361338232</v>
       </c>
       <c r="E71">
-        <v>35.65954</v>
+        <v>36.1802</v>
       </c>
       <c r="F71">
-        <v>35.92554</v>
+        <v>36.4462</v>
       </c>
       <c r="G71">
         <v>1</v>
@@ -7109,37 +7109,37 @@
         <v>4.076000000000001</v>
       </c>
       <c r="M71">
-        <v>7.213848432</v>
+        <v>7.318396959999999</v>
       </c>
       <c r="N71">
-        <v>-3.137848431999999</v>
+        <v>-3.242396959999999</v>
       </c>
       <c r="O71">
-        <v>-0.9413545295999998</v>
+        <v>-0.9727190879999996</v>
       </c>
       <c r="P71">
-        <v>-2.196493902399999</v>
+        <v>-2.269677871999999</v>
       </c>
       <c r="Q71">
-        <v>-1.742493902399999</v>
+        <v>-1.815677871999999</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.1940279068543584</v>
+        <v>0.198968837082837</v>
       </c>
       <c r="T71">
-        <v>1.269688192395819</v>
+        <v>1.312011132142346</v>
       </c>
       <c r="U71">
         <v>0.2008</v>
       </c>
       <c r="V71">
-        <v>0.1695073041146479</v>
+        <v>0.1670857711987244</v>
       </c>
       <c r="W71">
-        <v>0.1667629333337787</v>
+        <v>0.1672491771432962</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7147,7 +7147,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.5650243470488265</v>
+        <v>0.5569525706624148</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7155,22 +7155,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.1767650751251584</v>
+        <v>0.1783150751251584</v>
       </c>
       <c r="C72">
-        <v>-12.4602638661768</v>
+        <v>-13.22675763347516</v>
       </c>
       <c r="D72">
-        <v>22.9859361338232</v>
+        <v>22.74010236652484</v>
       </c>
       <c r="E72">
-        <v>36.1802</v>
+        <v>36.70086000000001</v>
       </c>
       <c r="F72">
-        <v>36.4462</v>
+        <v>36.96686</v>
       </c>
       <c r="G72">
         <v>1</v>
@@ -7191,37 +7191,37 @@
         <v>4.076000000000001</v>
       </c>
       <c r="M72">
-        <v>7.318396959999999</v>
+        <v>7.422945488000001</v>
       </c>
       <c r="N72">
-        <v>-3.242396959999999</v>
+        <v>-3.346945488</v>
       </c>
       <c r="O72">
-        <v>-0.9727190879999996</v>
+        <v>-1.0040836464</v>
       </c>
       <c r="P72">
-        <v>-2.269677871999999</v>
+        <v>-2.3428618416</v>
       </c>
       <c r="Q72">
-        <v>-1.815677871999999</v>
+        <v>-1.8888618416</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.198968837082837</v>
+        <v>0.2042505211201762</v>
       </c>
       <c r="T72">
-        <v>1.312011132142346</v>
+        <v>1.357252895319669</v>
       </c>
       <c r="U72">
         <v>0.2008</v>
       </c>
       <c r="V72">
-        <v>0.1670857711987244</v>
+        <v>0.1647324504776156</v>
       </c>
       <c r="W72">
-        <v>0.1672491771432962</v>
+        <v>0.1677217239440948</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7229,7 +7229,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.5569525706624148</v>
+        <v>0.5491081682587187</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7237,22 +7237,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.1783150751251584</v>
+        <v>0.1798650751251584</v>
       </c>
       <c r="C73">
-        <v>-13.22675763347516</v>
+        <v>-13.98804867696888</v>
       </c>
       <c r="D73">
-        <v>22.74010236652484</v>
+        <v>22.49947132303112</v>
       </c>
       <c r="E73">
-        <v>36.70086</v>
+        <v>37.22152</v>
       </c>
       <c r="F73">
-        <v>36.96686</v>
+        <v>37.48752</v>
       </c>
       <c r="G73">
         <v>1</v>
@@ -7273,37 +7273,37 @@
         <v>4.076000000000001</v>
       </c>
       <c r="M73">
-        <v>7.422945488</v>
+        <v>7.527494015999999</v>
       </c>
       <c r="N73">
-        <v>-3.346945487999999</v>
+        <v>-3.451494015999999</v>
       </c>
       <c r="O73">
-        <v>-1.0040836464</v>
+        <v>-1.0354482048</v>
       </c>
       <c r="P73">
-        <v>-2.3428618416</v>
+        <v>-2.416045811199999</v>
       </c>
       <c r="Q73">
-        <v>-1.8888618416</v>
+        <v>-1.962045811199999</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.2042505211201762</v>
+        <v>0.2099094683030396</v>
       </c>
       <c r="T73">
-        <v>1.357252895319669</v>
+        <v>1.405726213009656</v>
       </c>
       <c r="U73">
         <v>0.2008</v>
       </c>
       <c r="V73">
-        <v>0.1647324504776156</v>
+        <v>0.1624444997765376</v>
       </c>
       <c r="W73">
-        <v>0.1677217239440948</v>
+        <v>0.1681811444448713</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7311,7 +7311,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.5491081682587187</v>
+        <v>0.541481665921792</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7319,22 +7319,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.1798650751251584</v>
+        <v>0.1814150751251584</v>
       </c>
       <c r="C74">
-        <v>-13.98804867696888</v>
+        <v>-14.74430042967412</v>
       </c>
       <c r="D74">
-        <v>22.49947132303112</v>
+        <v>22.26387957032588</v>
       </c>
       <c r="E74">
-        <v>37.22152</v>
+        <v>37.74218</v>
       </c>
       <c r="F74">
-        <v>37.48752</v>
+        <v>38.00818</v>
       </c>
       <c r="G74">
         <v>1</v>
@@ -7355,37 +7355,37 @@
         <v>4.076000000000001</v>
       </c>
       <c r="M74">
-        <v>7.527494015999999</v>
+        <v>7.632042543999999</v>
       </c>
       <c r="N74">
-        <v>-3.451494015999999</v>
+        <v>-3.556042543999999</v>
       </c>
       <c r="O74">
-        <v>-1.0354482048</v>
+        <v>-1.0668127632</v>
       </c>
       <c r="P74">
-        <v>-2.416045811199999</v>
+        <v>-2.489229780799999</v>
       </c>
       <c r="Q74">
-        <v>-1.962045811199999</v>
+        <v>-2.035229780799999</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.2099094683030396</v>
+        <v>0.2159875967587077</v>
       </c>
       <c r="T74">
-        <v>1.405726213009656</v>
+        <v>1.457790146824829</v>
       </c>
       <c r="U74">
         <v>0.2008</v>
       </c>
       <c r="V74">
-        <v>0.1624444997765376</v>
+        <v>0.1602192326563111</v>
       </c>
       <c r="W74">
-        <v>0.1681811444448713</v>
+        <v>0.1686279780826127</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7393,7 +7393,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.541481665921792</v>
+        <v>0.5340641088543703</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7401,22 +7401,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.1814150751251584</v>
+        <v>0.1829650751251584</v>
       </c>
       <c r="C75">
-        <v>-14.74430042967412</v>
+        <v>-15.49566955031823</v>
       </c>
       <c r="D75">
-        <v>22.26387957032588</v>
+        <v>22.03317044968176</v>
       </c>
       <c r="E75">
-        <v>37.74218</v>
+        <v>38.26284</v>
       </c>
       <c r="F75">
-        <v>38.00818</v>
+        <v>38.52884</v>
       </c>
       <c r="G75">
         <v>1</v>
@@ -7437,37 +7437,37 @@
         <v>4.076000000000001</v>
       </c>
       <c r="M75">
-        <v>7.632042543999999</v>
+        <v>7.736591072</v>
       </c>
       <c r="N75">
-        <v>-3.556042543999999</v>
+        <v>-3.660591071999999</v>
       </c>
       <c r="O75">
-        <v>-1.0668127632</v>
+        <v>-1.0981773216</v>
       </c>
       <c r="P75">
-        <v>-2.489229780799999</v>
+        <v>-2.562413750399999</v>
       </c>
       <c r="Q75">
-        <v>-2.035229780799999</v>
+        <v>-2.108413750399999</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.2159875967587077</v>
+        <v>0.2225332735571196</v>
       </c>
       <c r="T75">
-        <v>1.457790146824829</v>
+        <v>1.513858998625784</v>
       </c>
       <c r="U75">
         <v>0.2008</v>
       </c>
       <c r="V75">
-        <v>0.1602192326563111</v>
+        <v>0.1580541078906852</v>
       </c>
       <c r="W75">
-        <v>0.1686279780826127</v>
+        <v>0.1690627351355504</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7475,7 +7475,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.5340641088543703</v>
+        <v>0.5268470263022842</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7483,22 +7483,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.1829650751251584</v>
+        <v>0.1845150751251584</v>
       </c>
       <c r="C76">
-        <v>-15.49566955031823</v>
+        <v>-16.24230627073225</v>
       </c>
       <c r="D76">
-        <v>22.03317044968176</v>
+        <v>21.80719372926774</v>
       </c>
       <c r="E76">
-        <v>38.26284</v>
+        <v>38.7835</v>
       </c>
       <c r="F76">
-        <v>38.52884</v>
+        <v>39.04949999999999</v>
       </c>
       <c r="G76">
         <v>1</v>
@@ -7519,37 +7519,37 @@
         <v>4.076000000000001</v>
       </c>
       <c r="M76">
-        <v>7.736591072</v>
+        <v>7.841139599999999</v>
       </c>
       <c r="N76">
-        <v>-3.660591071999999</v>
+        <v>-3.765139599999999</v>
       </c>
       <c r="O76">
-        <v>-1.0981773216</v>
+        <v>-1.129541879999999</v>
       </c>
       <c r="P76">
-        <v>-2.562413750399999</v>
+        <v>-2.635597719999999</v>
       </c>
       <c r="Q76">
-        <v>-2.108413750399999</v>
+        <v>-2.181597719999999</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.2225332735571196</v>
+        <v>0.2296026044994043</v>
       </c>
       <c r="T76">
-        <v>1.513858998625784</v>
+        <v>1.574413358570815</v>
       </c>
       <c r="U76">
         <v>0.2008</v>
       </c>
       <c r="V76">
-        <v>0.1580541078906852</v>
+        <v>0.1559467197854761</v>
       </c>
       <c r="W76">
-        <v>0.1690627351355504</v>
+        <v>0.1694858986670764</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7557,7 +7557,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.5268470263022842</v>
+        <v>0.5198223992849205</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7565,22 +7565,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.1845150751251584</v>
+        <v>0.1860650751251584</v>
       </c>
       <c r="C77">
-        <v>-16.24230627073225</v>
+        <v>-16.98435472208289</v>
       </c>
       <c r="D77">
-        <v>21.80719372926774</v>
+        <v>21.58580527791711</v>
       </c>
       <c r="E77">
-        <v>38.7835</v>
+        <v>39.30416</v>
       </c>
       <c r="F77">
-        <v>39.04949999999999</v>
+        <v>39.57015999999999</v>
       </c>
       <c r="G77">
         <v>1</v>
@@ -7601,37 +7601,37 @@
         <v>4.076000000000001</v>
       </c>
       <c r="M77">
-        <v>7.841139599999999</v>
+        <v>7.945688127999999</v>
       </c>
       <c r="N77">
-        <v>-3.765139599999999</v>
+        <v>-3.869688127999998</v>
       </c>
       <c r="O77">
-        <v>-1.129541879999999</v>
+        <v>-1.160906438399999</v>
       </c>
       <c r="P77">
-        <v>-2.635597719999999</v>
+        <v>-2.708781689599999</v>
       </c>
       <c r="Q77">
-        <v>-2.181597719999999</v>
+        <v>-2.254781689599998</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.2296026044994043</v>
+        <v>0.2372610463535462</v>
       </c>
       <c r="T77">
-        <v>1.574413358570815</v>
+        <v>1.640013915177932</v>
       </c>
       <c r="U77">
         <v>0.2008</v>
       </c>
       <c r="V77">
-        <v>0.1559467197854761</v>
+        <v>0.153894789261983</v>
       </c>
       <c r="W77">
-        <v>0.1694858986670764</v>
+        <v>0.1698979263161938</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7639,7 +7639,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.5198223992849205</v>
+        <v>0.5129826308732768</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7647,22 +7647,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.1860650751251584</v>
+        <v>0.1876150751251584</v>
       </c>
       <c r="C78">
-        <v>-16.98435472208289</v>
+        <v>-17.7219532414325</v>
       </c>
       <c r="D78">
-        <v>21.58580527791711</v>
+        <v>21.3688667585675</v>
       </c>
       <c r="E78">
-        <v>39.30416</v>
+        <v>39.82482</v>
       </c>
       <c r="F78">
-        <v>39.57015999999999</v>
+        <v>40.09082</v>
       </c>
       <c r="G78">
         <v>1</v>
@@ -7683,37 +7683,37 @@
         <v>4.076000000000001</v>
       </c>
       <c r="M78">
-        <v>7.945688127999999</v>
+        <v>8.050236656000001</v>
       </c>
       <c r="N78">
-        <v>-3.869688127999998</v>
+        <v>-3.974236656</v>
       </c>
       <c r="O78">
-        <v>-1.160906438399999</v>
+        <v>-1.1922709968</v>
       </c>
       <c r="P78">
-        <v>-2.708781689599999</v>
+        <v>-2.7819656592</v>
       </c>
       <c r="Q78">
-        <v>-2.254781689599998</v>
+        <v>-2.3279656592</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.2372610463535462</v>
+        <v>0.2455854396732656</v>
       </c>
       <c r="T78">
-        <v>1.640013915177932</v>
+        <v>1.711318868011756</v>
       </c>
       <c r="U78">
         <v>0.2008</v>
       </c>
       <c r="V78">
-        <v>0.153894789261983</v>
+        <v>0.151896155635204</v>
       </c>
       <c r="W78">
-        <v>0.1698979263161938</v>
+        <v>0.1702992519484511</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7721,7 +7721,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.5129826308732768</v>
+        <v>0.5063205187840132</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7729,22 +7729,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.1876150751251584</v>
+        <v>0.2173684605174677</v>
       </c>
       <c r="C79">
-        <v>-17.7219532414325</v>
+        <v>-21.69837622261185</v>
       </c>
       <c r="D79">
-        <v>21.3688667585675</v>
+        <v>17.91310377738815</v>
       </c>
       <c r="E79">
-        <v>39.82482</v>
+        <v>40.34548</v>
       </c>
       <c r="F79">
-        <v>40.09082</v>
+        <v>40.61148</v>
       </c>
       <c r="G79">
         <v>1</v>
@@ -7765,45 +7765,45 @@
         <v>4.076000000000001</v>
       </c>
       <c r="M79">
-        <v>8.050236656000001</v>
+        <v>9.576186984</v>
       </c>
       <c r="N79">
-        <v>-3.974236656</v>
+        <v>-5.500186983999999</v>
       </c>
       <c r="O79">
-        <v>-1.1922709968</v>
+        <v>-1.6500560952</v>
       </c>
       <c r="P79">
-        <v>-2.7819656592</v>
+        <v>-3.850130888799999</v>
       </c>
       <c r="Q79">
-        <v>-2.3279656592</v>
+        <v>-3.396130888799999</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.2455854396732656</v>
+        <v>0.2587728932598202</v>
       </c>
       <c r="T79">
-        <v>1.711318868011756</v>
+        <v>1.824279743341852</v>
       </c>
       <c r="U79">
-        <v>0.2008</v>
+        <v>0.2358</v>
       </c>
       <c r="V79">
-        <v>0.151896155635204</v>
+        <v>0.1276917422396898</v>
       </c>
       <c r="W79">
-        <v>0.1702992519484511</v>
+        <v>0.2056902871798812</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y79">
-        <v>0.5063205187840132</v>
+        <v>0.4256391407989659</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7811,22 +7811,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.2173684605174677</v>
+        <v>0.2192684605174678</v>
       </c>
       <c r="C80">
-        <v>-21.69837622261185</v>
+        <v>-22.4021362869066</v>
       </c>
       <c r="D80">
-        <v>17.91310377738815</v>
+        <v>17.7300037130934</v>
       </c>
       <c r="E80">
-        <v>40.34548</v>
+        <v>40.86614</v>
       </c>
       <c r="F80">
-        <v>40.61148</v>
+        <v>41.13214</v>
       </c>
       <c r="G80">
         <v>1</v>
@@ -7847,37 +7847,37 @@
         <v>4.076000000000001</v>
       </c>
       <c r="M80">
-        <v>9.576186984</v>
+        <v>9.698958612</v>
       </c>
       <c r="N80">
-        <v>-5.500186983999999</v>
+        <v>-5.622958612</v>
       </c>
       <c r="O80">
-        <v>-1.6500560952</v>
+        <v>-1.6868875836</v>
       </c>
       <c r="P80">
-        <v>-3.850130888799999</v>
+        <v>-3.9360710284</v>
       </c>
       <c r="Q80">
-        <v>-3.396130888799999</v>
+        <v>-3.4820710284</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.2587728932598202</v>
+        <v>0.268914459605526</v>
       </c>
       <c r="T80">
-        <v>1.824279743341852</v>
+        <v>1.911150207310512</v>
       </c>
       <c r="U80">
         <v>0.2358</v>
       </c>
       <c r="V80">
-        <v>0.1276917422396898</v>
+        <v>0.1260753910720988</v>
       </c>
       <c r="W80">
-        <v>0.2056902871798812</v>
+        <v>0.2060714227851991</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -7885,7 +7885,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.4256391407989659</v>
+        <v>0.4202513035736625</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7893,22 +7893,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.2192684605174678</v>
+        <v>0.2211684605174678</v>
       </c>
       <c r="C81">
-        <v>-22.4021362869066</v>
+        <v>-23.10219108419198</v>
       </c>
       <c r="D81">
-        <v>17.7300037130934</v>
+        <v>17.55060891580802</v>
       </c>
       <c r="E81">
-        <v>40.86614</v>
+        <v>41.3868</v>
       </c>
       <c r="F81">
-        <v>41.13214</v>
+        <v>41.6528</v>
       </c>
       <c r="G81">
         <v>1</v>
@@ -7929,37 +7929,37 @@
         <v>4.076000000000001</v>
       </c>
       <c r="M81">
-        <v>9.698958612</v>
+        <v>9.821730240000001</v>
       </c>
       <c r="N81">
-        <v>-5.622958612</v>
+        <v>-5.74573024</v>
       </c>
       <c r="O81">
-        <v>-1.6868875836</v>
+        <v>-1.723719072</v>
       </c>
       <c r="P81">
-        <v>-3.9360710284</v>
+        <v>-4.022011168000001</v>
       </c>
       <c r="Q81">
-        <v>-3.4820710284</v>
+        <v>-3.568011168</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.268914459605526</v>
+        <v>0.2800701825858022</v>
       </c>
       <c r="T81">
-        <v>1.911150207310512</v>
+        <v>2.006707717676037</v>
       </c>
       <c r="U81">
         <v>0.2358</v>
       </c>
       <c r="V81">
-        <v>0.1260753910720988</v>
+        <v>0.1244994486836975</v>
       </c>
       <c r="W81">
-        <v>0.2060714227851991</v>
+        <v>0.2064430300003841</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -7967,7 +7967,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.4202513035736625</v>
+        <v>0.4149981622789917</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7975,22 +7975,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.2211684605174678</v>
+        <v>0.2230684605174678</v>
       </c>
       <c r="C82">
-        <v>-23.10219108419198</v>
+        <v>-23.79865195918293</v>
       </c>
       <c r="D82">
-        <v>17.55060891580802</v>
+        <v>17.37480804081707</v>
       </c>
       <c r="E82">
-        <v>41.3868</v>
+        <v>41.90746</v>
       </c>
       <c r="F82">
-        <v>41.6528</v>
+        <v>42.17346</v>
       </c>
       <c r="G82">
         <v>1</v>
@@ -8011,37 +8011,37 @@
         <v>4.076000000000001</v>
       </c>
       <c r="M82">
-        <v>9.821730240000001</v>
+        <v>9.944501868</v>
       </c>
       <c r="N82">
-        <v>-5.74573024</v>
+        <v>-5.868501867999999</v>
       </c>
       <c r="O82">
-        <v>-1.723719072</v>
+        <v>-1.7605505604</v>
       </c>
       <c r="P82">
-        <v>-4.022011168000001</v>
+        <v>-4.1079513076</v>
       </c>
       <c r="Q82">
-        <v>-3.568011168</v>
+        <v>-3.653951307599999</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.2800701825858022</v>
+        <v>0.2924001921955813</v>
       </c>
       <c r="T82">
-        <v>2.006707717676037</v>
+        <v>2.112323913343197</v>
       </c>
       <c r="U82">
         <v>0.2358</v>
       </c>
       <c r="V82">
-        <v>0.1244994486836975</v>
+        <v>0.1229624184530346</v>
       </c>
       <c r="W82">
-        <v>0.2064430300003841</v>
+        <v>0.2068054617287745</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8049,7 +8049,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.4149981622789917</v>
+        <v>0.4098747281767819</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8057,22 +8057,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.2230684605174678</v>
+        <v>0.2249684605174678</v>
       </c>
       <c r="C83">
-        <v>-23.79865195918293</v>
+        <v>-24.49162583956952</v>
       </c>
       <c r="D83">
-        <v>17.37480804081707</v>
+        <v>17.20249416043048</v>
       </c>
       <c r="E83">
-        <v>41.90746</v>
+        <v>42.42812</v>
       </c>
       <c r="F83">
-        <v>42.17346</v>
+        <v>42.69412</v>
       </c>
       <c r="G83">
         <v>1</v>
@@ -8093,37 +8093,37 @@
         <v>4.076000000000001</v>
       </c>
       <c r="M83">
-        <v>9.944501868</v>
+        <v>10.067273496</v>
       </c>
       <c r="N83">
-        <v>-5.868501867999999</v>
+        <v>-5.991273496</v>
       </c>
       <c r="O83">
-        <v>-1.7605505604</v>
+        <v>-1.7973820488</v>
       </c>
       <c r="P83">
-        <v>-4.1079513076</v>
+        <v>-4.1938914472</v>
       </c>
       <c r="Q83">
-        <v>-3.653951307599999</v>
+        <v>-3.7398914472</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.2924001921955813</v>
+        <v>0.3061002028731137</v>
       </c>
       <c r="T83">
-        <v>2.112323913343197</v>
+        <v>2.229675241862264</v>
       </c>
       <c r="U83">
         <v>0.2358</v>
       </c>
       <c r="V83">
-        <v>0.1229624184530346</v>
+        <v>0.1214628767645829</v>
       </c>
       <c r="W83">
-        <v>0.2068054617287745</v>
+        <v>0.2071590536589114</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8131,7 +8131,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.4098747281767819</v>
+        <v>0.4048762558819432</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8139,22 +8139,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.2249684605174678</v>
+        <v>0.2268684605174677</v>
       </c>
       <c r="C84">
-        <v>-24.49162583956952</v>
+        <v>-25.18121545289429</v>
       </c>
       <c r="D84">
-        <v>17.20249416043048</v>
+        <v>17.03356454710571</v>
       </c>
       <c r="E84">
-        <v>42.42812</v>
+        <v>42.94878</v>
       </c>
       <c r="F84">
-        <v>42.69412</v>
+        <v>43.21478</v>
       </c>
       <c r="G84">
         <v>1</v>
@@ -8175,37 +8175,37 @@
         <v>4.076000000000001</v>
       </c>
       <c r="M84">
-        <v>10.067273496</v>
+        <v>10.190045124</v>
       </c>
       <c r="N84">
-        <v>-5.991273496</v>
+        <v>-6.114045123999999</v>
       </c>
       <c r="O84">
-        <v>-1.7973820488</v>
+        <v>-1.834213537199999</v>
       </c>
       <c r="P84">
-        <v>-4.1938914472</v>
+        <v>-4.279831586799999</v>
       </c>
       <c r="Q84">
-        <v>-3.7398914472</v>
+        <v>-3.825831586799999</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.3061002028731137</v>
+        <v>0.3214119795127086</v>
       </c>
       <c r="T84">
-        <v>2.229675241862264</v>
+        <v>2.360832609030633</v>
       </c>
       <c r="U84">
         <v>0.2358</v>
       </c>
       <c r="V84">
-        <v>0.1214628767645829</v>
+        <v>0.1199994686107928</v>
       </c>
       <c r="W84">
-        <v>0.2071590536589114</v>
+        <v>0.2075041253015751</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8213,7 +8213,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.4048762558819432</v>
+        <v>0.3999982287026427</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8221,22 +8221,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.2268684605174677</v>
+        <v>0.2287684605174677</v>
       </c>
       <c r="C85">
-        <v>-25.18121545289429</v>
+        <v>-25.86751953077536</v>
       </c>
       <c r="D85">
-        <v>17.03356454710571</v>
+        <v>16.86792046922464</v>
       </c>
       <c r="E85">
-        <v>42.94878</v>
+        <v>43.46944</v>
       </c>
       <c r="F85">
-        <v>43.21478</v>
+        <v>43.73544</v>
       </c>
       <c r="G85">
         <v>1</v>
@@ -8257,37 +8257,37 @@
         <v>4.076000000000001</v>
       </c>
       <c r="M85">
-        <v>10.190045124</v>
+        <v>10.312816752</v>
       </c>
       <c r="N85">
-        <v>-6.114045123999999</v>
+        <v>-6.236816751999999</v>
       </c>
       <c r="O85">
-        <v>-1.834213537199999</v>
+        <v>-1.8710450256</v>
       </c>
       <c r="P85">
-        <v>-4.279831586799999</v>
+        <v>-4.365771726399999</v>
       </c>
       <c r="Q85">
-        <v>-3.825831586799999</v>
+        <v>-3.911771726399999</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.3214119795127086</v>
+        <v>0.3386377282322529</v>
       </c>
       <c r="T85">
-        <v>2.360832609030633</v>
+        <v>2.508384647095048</v>
       </c>
       <c r="U85">
         <v>0.2358</v>
       </c>
       <c r="V85">
-        <v>0.1199994686107928</v>
+        <v>0.1185709035082834</v>
       </c>
       <c r="W85">
-        <v>0.2075041253015751</v>
+        <v>0.2078409809527468</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8295,7 +8295,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.3999982287026427</v>
+        <v>0.3952363450276112</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8303,22 +8303,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.2287684605174677</v>
+        <v>0.2306684605174678</v>
       </c>
       <c r="C86">
-        <v>-25.86751953077536</v>
+        <v>-26.55063300132847</v>
       </c>
       <c r="D86">
-        <v>16.86792046922464</v>
+        <v>16.70546699867153</v>
       </c>
       <c r="E86">
-        <v>43.46944</v>
+        <v>43.9901</v>
       </c>
       <c r="F86">
-        <v>43.73544</v>
+        <v>44.2561</v>
       </c>
       <c r="G86">
         <v>1</v>
@@ -8339,37 +8339,37 @@
         <v>4.076000000000001</v>
       </c>
       <c r="M86">
-        <v>10.312816752</v>
+        <v>10.43558838</v>
       </c>
       <c r="N86">
-        <v>-6.236816751999999</v>
+        <v>-6.35958838</v>
       </c>
       <c r="O86">
-        <v>-1.8710450256</v>
+        <v>-1.907876514</v>
       </c>
       <c r="P86">
-        <v>-4.365771726399999</v>
+        <v>-4.451711866</v>
       </c>
       <c r="Q86">
-        <v>-3.911771726399999</v>
+        <v>-3.997711866</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.3386377282322527</v>
+        <v>0.3581602434477362</v>
       </c>
       <c r="T86">
-        <v>2.508384647095046</v>
+        <v>2.675610290234716</v>
       </c>
       <c r="U86">
         <v>0.2358</v>
       </c>
       <c r="V86">
-        <v>0.1185709035082834</v>
+        <v>0.1171759517023035</v>
       </c>
       <c r="W86">
-        <v>0.2078409809527468</v>
+        <v>0.2081699105885968</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8377,7 +8377,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.3952363450276112</v>
+        <v>0.3905865056743452</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8385,22 +8385,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.2306684605174678</v>
+        <v>0.2325684605174677</v>
       </c>
       <c r="C87">
-        <v>-26.55063300132847</v>
+        <v>-27.23064717057579</v>
       </c>
       <c r="D87">
-        <v>16.70546699867153</v>
+        <v>16.54611282942421</v>
       </c>
       <c r="E87">
-        <v>43.9901</v>
+        <v>44.51076</v>
       </c>
       <c r="F87">
-        <v>44.2561</v>
+        <v>44.77676</v>
       </c>
       <c r="G87">
         <v>1</v>
@@ -8421,37 +8421,37 @@
         <v>4.076000000000001</v>
       </c>
       <c r="M87">
-        <v>10.43558838</v>
+        <v>10.558360008</v>
       </c>
       <c r="N87">
-        <v>-6.35958838</v>
+        <v>-6.482360007999999</v>
       </c>
       <c r="O87">
-        <v>-1.907876514</v>
+        <v>-1.9447080024</v>
       </c>
       <c r="P87">
-        <v>-4.451711866</v>
+        <v>-4.537652005599999</v>
       </c>
       <c r="Q87">
-        <v>-3.997711866</v>
+        <v>-4.083652005599999</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.3581602434477362</v>
+        <v>0.3804716894082888</v>
       </c>
       <c r="T87">
-        <v>2.675610290234716</v>
+        <v>2.866725310965767</v>
       </c>
       <c r="U87">
         <v>0.2358</v>
       </c>
       <c r="V87">
-        <v>0.1171759517023035</v>
+        <v>0.1158134406359977</v>
       </c>
       <c r="W87">
-        <v>0.2081699105885968</v>
+        <v>0.2084911906980317</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8459,7 +8459,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.3905865056743452</v>
+        <v>0.3860448021199924</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8467,22 +8467,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.2325684605174677</v>
+        <v>0.2344684605174678</v>
       </c>
       <c r="C88">
-        <v>-27.23064717057579</v>
+        <v>-27.90764989357015</v>
       </c>
       <c r="D88">
-        <v>16.54611282942421</v>
+        <v>16.38977010642984</v>
       </c>
       <c r="E88">
-        <v>44.51076</v>
+        <v>45.03142</v>
       </c>
       <c r="F88">
-        <v>44.77676</v>
+        <v>45.29742</v>
       </c>
       <c r="G88">
         <v>1</v>
@@ -8503,37 +8503,37 @@
         <v>4.076000000000001</v>
       </c>
       <c r="M88">
-        <v>10.558360008</v>
+        <v>10.681131636</v>
       </c>
       <c r="N88">
-        <v>-6.482360007999999</v>
+        <v>-6.605131635999999</v>
       </c>
       <c r="O88">
-        <v>-1.9447080024</v>
+        <v>-1.9815394908</v>
       </c>
       <c r="P88">
-        <v>-4.537652005599999</v>
+        <v>-4.6235921452</v>
       </c>
       <c r="Q88">
-        <v>-4.083652005599999</v>
+        <v>-4.1695921452</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.3804716894082888</v>
+        <v>0.4062156655166187</v>
       </c>
       <c r="T88">
-        <v>2.866725310965767</v>
+        <v>3.087242642578518</v>
       </c>
       <c r="U88">
         <v>0.2358</v>
       </c>
       <c r="V88">
-        <v>0.1158134406359977</v>
+        <v>0.1144822516631701</v>
       </c>
       <c r="W88">
-        <v>0.2084911906980317</v>
+        <v>0.2088050850578245</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8541,7 +8541,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.3860448021199924</v>
+        <v>0.3816075055439004</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8549,22 +8549,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.2344684605174678</v>
+        <v>0.2363684605174677</v>
       </c>
       <c r="C89">
-        <v>-27.90764989357015</v>
+        <v>-28.58172573590836</v>
       </c>
       <c r="D89">
-        <v>16.38977010642984</v>
+        <v>16.23635426409164</v>
       </c>
       <c r="E89">
-        <v>45.03142</v>
+        <v>45.55208</v>
       </c>
       <c r="F89">
-        <v>45.29742</v>
+        <v>45.81807999999999</v>
       </c>
       <c r="G89">
         <v>1</v>
@@ -8585,37 +8585,37 @@
         <v>4.076000000000001</v>
       </c>
       <c r="M89">
-        <v>10.681131636</v>
+        <v>10.803903264</v>
       </c>
       <c r="N89">
-        <v>-6.605131635999999</v>
+        <v>-6.727903263999998</v>
       </c>
       <c r="O89">
-        <v>-1.9815394908</v>
+        <v>-2.018370979199999</v>
       </c>
       <c r="P89">
-        <v>-4.6235921452</v>
+        <v>-4.709532284799999</v>
       </c>
       <c r="Q89">
-        <v>-4.1695921452</v>
+        <v>-4.255532284799999</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.4062156655166187</v>
+        <v>0.4362503043096703</v>
       </c>
       <c r="T89">
-        <v>3.087242642578518</v>
+        <v>3.344512862793395</v>
       </c>
       <c r="U89">
         <v>0.2358</v>
       </c>
       <c r="V89">
-        <v>0.1144822516631701</v>
+        <v>0.1131813169851796</v>
       </c>
       <c r="W89">
-        <v>0.2088050850578245</v>
+        <v>0.2091118454548946</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8623,7 +8623,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.3816075055439004</v>
+        <v>0.3772710566172652</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8631,22 +8631,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.2363684605174677</v>
+        <v>0.2382684605174677</v>
       </c>
       <c r="C90">
-        <v>-28.58172573590836</v>
+        <v>-29.25295612625767</v>
       </c>
       <c r="D90">
-        <v>16.23635426409164</v>
+        <v>16.08578387374233</v>
       </c>
       <c r="E90">
-        <v>45.55208</v>
+        <v>46.07274</v>
       </c>
       <c r="F90">
-        <v>45.81807999999999</v>
+        <v>46.33873999999999</v>
       </c>
       <c r="G90">
         <v>1</v>
@@ -8667,37 +8667,37 @@
         <v>4.076000000000001</v>
       </c>
       <c r="M90">
-        <v>10.803903264</v>
+        <v>10.926674892</v>
       </c>
       <c r="N90">
-        <v>-6.727903263999998</v>
+        <v>-6.850674891999999</v>
       </c>
       <c r="O90">
-        <v>-2.018370979199999</v>
+        <v>-2.0552024676</v>
       </c>
       <c r="P90">
-        <v>-4.709532284799999</v>
+        <v>-4.7954724244</v>
       </c>
       <c r="Q90">
-        <v>-4.255532284799999</v>
+        <v>-4.3414724244</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.4362503043096703</v>
+        <v>0.4717457865196404</v>
       </c>
       <c r="T90">
-        <v>3.344512862793395</v>
+        <v>3.648559486683704</v>
       </c>
       <c r="U90">
         <v>0.2358</v>
       </c>
       <c r="V90">
-        <v>0.1131813169851796</v>
+        <v>0.1119096167943349</v>
       </c>
       <c r="W90">
-        <v>0.2091118454548946</v>
+        <v>0.2094117123598958</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8705,7 +8705,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.3772710566172652</v>
+        <v>0.3730320559811162</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8713,22 +8713,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.2382684605174677</v>
+        <v>0.2401684605174678</v>
       </c>
       <c r="C91">
-        <v>-29.25295612625767</v>
+        <v>-29.92141950047332</v>
       </c>
       <c r="D91">
-        <v>16.08578387374233</v>
+        <v>15.93798049952667</v>
       </c>
       <c r="E91">
-        <v>46.07274</v>
+        <v>46.5934</v>
       </c>
       <c r="F91">
-        <v>46.33873999999999</v>
+        <v>46.85939999999999</v>
       </c>
       <c r="G91">
         <v>1</v>
@@ -8749,37 +8749,37 @@
         <v>4.076000000000001</v>
       </c>
       <c r="M91">
-        <v>10.926674892</v>
+        <v>11.04944652</v>
       </c>
       <c r="N91">
-        <v>-6.850674891999999</v>
+        <v>-6.973446519999998</v>
       </c>
       <c r="O91">
-        <v>-2.0552024676</v>
+        <v>-2.092033955999999</v>
       </c>
       <c r="P91">
-        <v>-4.7954724244</v>
+        <v>-4.881412563999998</v>
       </c>
       <c r="Q91">
-        <v>-4.3414724244</v>
+        <v>-4.427412563999998</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.4717457865196404</v>
+        <v>0.5143403651716044</v>
       </c>
       <c r="T91">
-        <v>3.648559486683704</v>
+        <v>4.013415435352075</v>
       </c>
       <c r="U91">
         <v>0.2358</v>
       </c>
       <c r="V91">
-        <v>0.1119096167943349</v>
+        <v>0.1106661766077311</v>
       </c>
       <c r="W91">
-        <v>0.2094117123598958</v>
+        <v>0.209704915555897</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8787,7 +8787,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.3730320559811162</v>
+        <v>0.3688872553591038</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8795,22 +8795,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.2401684605174678</v>
+        <v>0.2420684605174678</v>
       </c>
       <c r="C92">
-        <v>-29.92141950047332</v>
+        <v>-30.58719143784316</v>
       </c>
       <c r="D92">
-        <v>15.93798049952667</v>
+        <v>15.79286856215684</v>
       </c>
       <c r="E92">
-        <v>46.5934</v>
+        <v>47.11406</v>
       </c>
       <c r="F92">
-        <v>46.85939999999999</v>
+        <v>47.38006</v>
       </c>
       <c r="G92">
         <v>1</v>
@@ -8831,37 +8831,37 @@
         <v>4.076000000000001</v>
       </c>
       <c r="M92">
-        <v>11.04944652</v>
+        <v>11.172218148</v>
       </c>
       <c r="N92">
-        <v>-6.973446519999998</v>
+        <v>-7.096218148</v>
       </c>
       <c r="O92">
-        <v>-2.092033955999999</v>
+        <v>-2.1288654444</v>
       </c>
       <c r="P92">
-        <v>-4.881412563999998</v>
+        <v>-4.9673527036</v>
       </c>
       <c r="Q92">
-        <v>-4.427412563999998</v>
+        <v>-4.5133527036</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.5143403651716044</v>
+        <v>0.5664004057462273</v>
       </c>
       <c r="T92">
-        <v>4.013415435352075</v>
+        <v>4.459350483724529</v>
       </c>
       <c r="U92">
         <v>0.2358</v>
       </c>
       <c r="V92">
-        <v>0.1106661766077311</v>
+        <v>0.1094500647768769</v>
       </c>
       <c r="W92">
-        <v>0.209704915555897</v>
+        <v>0.2099916747256124</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8869,7 +8869,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.3688872553591038</v>
+        <v>0.3648335492562564</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8877,22 +8877,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.2420684605174678</v>
+        <v>0.2439684605174678</v>
       </c>
       <c r="C93">
-        <v>-30.58719143784316</v>
+        <v>-31.25034478995646</v>
       </c>
       <c r="D93">
-        <v>15.79286856215684</v>
+        <v>15.65037521004353</v>
       </c>
       <c r="E93">
-        <v>47.11406</v>
+        <v>47.63472</v>
       </c>
       <c r="F93">
-        <v>47.38006</v>
+        <v>47.90072</v>
       </c>
       <c r="G93">
         <v>1</v>
@@ -8913,37 +8913,37 @@
         <v>4.076000000000001</v>
       </c>
       <c r="M93">
-        <v>11.172218148</v>
+        <v>11.294989776</v>
       </c>
       <c r="N93">
-        <v>-7.096218148</v>
+        <v>-7.218989775999999</v>
       </c>
       <c r="O93">
-        <v>-2.1288654444</v>
+        <v>-2.1656969328</v>
       </c>
       <c r="P93">
-        <v>-4.9673527036</v>
+        <v>-5.053292843199999</v>
       </c>
       <c r="Q93">
-        <v>-4.5133527036</v>
+        <v>-4.5992928432</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.5664004057462273</v>
+        <v>0.6314754564645058</v>
       </c>
       <c r="T93">
-        <v>4.459350483724529</v>
+        <v>5.016769294190095</v>
       </c>
       <c r="U93">
         <v>0.2358</v>
       </c>
       <c r="V93">
-        <v>0.1094500647768769</v>
+        <v>0.108260390159737</v>
       </c>
       <c r="W93">
-        <v>0.2099916747256124</v>
+        <v>0.210272200000334</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8951,7 +8951,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.3648335492562564</v>
+        <v>0.3608679671991233</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8959,22 +8959,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.2439684605174678</v>
+        <v>0.2458684605174677</v>
       </c>
       <c r="C94">
-        <v>-31.25034478995646</v>
+        <v>-31.91094980265888</v>
       </c>
       <c r="D94">
-        <v>15.65037521004353</v>
+        <v>15.51043019734112</v>
       </c>
       <c r="E94">
-        <v>47.63472</v>
+        <v>48.15538</v>
       </c>
       <c r="F94">
-        <v>47.90072</v>
+        <v>48.42138</v>
       </c>
       <c r="G94">
         <v>1</v>
@@ -8995,37 +8995,37 @@
         <v>4.076000000000001</v>
       </c>
       <c r="M94">
-        <v>11.294989776</v>
+        <v>11.417761404</v>
       </c>
       <c r="N94">
-        <v>-7.218989775999999</v>
+        <v>-7.341761404</v>
       </c>
       <c r="O94">
-        <v>-2.1656969328</v>
+        <v>-2.2025284212</v>
       </c>
       <c r="P94">
-        <v>-5.053292843199999</v>
+        <v>-5.139232982799999</v>
       </c>
       <c r="Q94">
-        <v>-4.5992928432</v>
+        <v>-4.6852329828</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.6314754564645058</v>
+        <v>0.7151433788165781</v>
       </c>
       <c r="T94">
-        <v>5.016769294190095</v>
+        <v>5.733450621931538</v>
       </c>
       <c r="U94">
         <v>0.2358</v>
       </c>
       <c r="V94">
-        <v>0.108260390159737</v>
+        <v>0.1070962999429656</v>
       </c>
       <c r="W94">
-        <v>0.210272200000334</v>
+        <v>0.2105466924734487</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9033,7 +9033,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.3608679671991233</v>
+        <v>0.356987666476552</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9041,22 +9041,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.2458684605174677</v>
+        <v>0.2477684605174678</v>
       </c>
       <c r="C95">
-        <v>-31.91094980265888</v>
+        <v>-32.56907423152209</v>
       </c>
       <c r="D95">
-        <v>15.51043019734112</v>
+        <v>15.37296576847791</v>
       </c>
       <c r="E95">
-        <v>48.15538</v>
+        <v>48.67604</v>
       </c>
       <c r="F95">
-        <v>48.42138</v>
+        <v>48.94204</v>
       </c>
       <c r="G95">
         <v>1</v>
@@ -9077,37 +9077,37 @@
         <v>4.076000000000001</v>
       </c>
       <c r="M95">
-        <v>11.417761404</v>
+        <v>11.540533032</v>
       </c>
       <c r="N95">
-        <v>-7.341761404</v>
+        <v>-7.464533032</v>
       </c>
       <c r="O95">
-        <v>-2.2025284212</v>
+        <v>-2.2393599096</v>
       </c>
       <c r="P95">
-        <v>-5.139232982799999</v>
+        <v>-5.2251731224</v>
       </c>
       <c r="Q95">
-        <v>-4.6852329828</v>
+        <v>-4.7711731224</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.7151433788165781</v>
+        <v>0.8267006086193414</v>
       </c>
       <c r="T95">
-        <v>5.733450621931538</v>
+        <v>6.689025725586796</v>
       </c>
       <c r="U95">
         <v>0.2358</v>
       </c>
       <c r="V95">
-        <v>0.1070962999429656</v>
+        <v>0.1059569776031468</v>
       </c>
       <c r="W95">
-        <v>0.2105466924734487</v>
+        <v>0.210815344681178</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9115,7 +9115,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.356987666476552</v>
+        <v>0.3531899253438228</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9123,22 +9123,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2477684605174678</v>
+        <v>0.2496684605174678</v>
       </c>
       <c r="C96">
-        <v>-32.56907423152209</v>
+        <v>-33.22478345122724</v>
       </c>
       <c r="D96">
-        <v>15.37296576847791</v>
+        <v>15.23791654877276</v>
       </c>
       <c r="E96">
-        <v>48.67604</v>
+        <v>49.1967</v>
       </c>
       <c r="F96">
-        <v>48.94204</v>
+        <v>49.4627</v>
       </c>
       <c r="G96">
         <v>1</v>
@@ -9159,37 +9159,37 @@
         <v>4.076000000000001</v>
       </c>
       <c r="M96">
-        <v>11.540533032</v>
+        <v>11.66330466</v>
       </c>
       <c r="N96">
-        <v>-7.464533032</v>
+        <v>-7.587304659999999</v>
       </c>
       <c r="O96">
-        <v>-2.2393599096</v>
+        <v>-2.276191397999999</v>
       </c>
       <c r="P96">
-        <v>-5.2251731224</v>
+        <v>-5.311113261999999</v>
       </c>
       <c r="Q96">
-        <v>-4.7711731224</v>
+        <v>-4.857113261999999</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.8267006086193414</v>
+        <v>0.9828807303432101</v>
       </c>
       <c r="T96">
-        <v>6.689025725586796</v>
+        <v>8.02683087070416</v>
       </c>
       <c r="U96">
         <v>0.2358</v>
       </c>
       <c r="V96">
-        <v>0.1059569776031468</v>
+        <v>0.1048416409967979</v>
       </c>
       <c r="W96">
-        <v>0.210815344681178</v>
+        <v>0.2110783410529551</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9197,7 +9197,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.3531899253438228</v>
+        <v>0.3494721366559931</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9205,22 +9205,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2496684605174678</v>
+        <v>0.2515684605174678</v>
       </c>
       <c r="C97">
-        <v>-33.22478345122724</v>
+        <v>-33.87814055923314</v>
       </c>
       <c r="D97">
-        <v>15.23791654877276</v>
+        <v>15.10521944076686</v>
       </c>
       <c r="E97">
-        <v>49.1967</v>
+        <v>49.71736</v>
       </c>
       <c r="F97">
-        <v>49.4627</v>
+        <v>49.98336</v>
       </c>
       <c r="G97">
         <v>1</v>
@@ -9241,37 +9241,37 @@
         <v>4.076000000000001</v>
       </c>
       <c r="M97">
-        <v>11.66330466</v>
+        <v>11.786076288</v>
       </c>
       <c r="N97">
-        <v>-7.587304659999999</v>
+        <v>-7.710076288</v>
       </c>
       <c r="O97">
-        <v>-2.276191397999999</v>
+        <v>-2.3130228864</v>
       </c>
       <c r="P97">
-        <v>-5.311113261999999</v>
+        <v>-5.3970534016</v>
       </c>
       <c r="Q97">
-        <v>-4.857113261999999</v>
+        <v>-4.9430534016</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.9828807303432101</v>
+        <v>1.217150912929013</v>
       </c>
       <c r="T97">
-        <v>8.02683087070416</v>
+        <v>10.0335385883802</v>
       </c>
       <c r="U97">
         <v>0.2358</v>
       </c>
       <c r="V97">
-        <v>0.1048416409967979</v>
+        <v>0.1037495405697479</v>
       </c>
       <c r="W97">
-        <v>0.2110783410529551</v>
+        <v>0.2113358583336535</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9279,7 +9279,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.3494721366559931</v>
+        <v>0.3458318018991597</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9287,22 +9287,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.2515684605174678</v>
+        <v>0.2534684605174677</v>
       </c>
       <c r="C98">
-        <v>-33.87814055923313</v>
+        <v>-34.52920647407443</v>
       </c>
       <c r="D98">
-        <v>15.10521944076686</v>
+        <v>14.97481352592557</v>
       </c>
       <c r="E98">
-        <v>49.71735999999999</v>
+        <v>50.23802</v>
       </c>
       <c r="F98">
-        <v>49.98335999999999</v>
+        <v>50.50402</v>
       </c>
       <c r="G98">
         <v>1</v>
@@ -9323,37 +9323,37 @@
         <v>4.076000000000001</v>
       </c>
       <c r="M98">
-        <v>11.786076288</v>
+        <v>11.908847916</v>
       </c>
       <c r="N98">
-        <v>-7.710076287999998</v>
+        <v>-7.832847915999999</v>
       </c>
       <c r="O98">
-        <v>-2.313022886399999</v>
+        <v>-2.3498543748</v>
       </c>
       <c r="P98">
-        <v>-5.397053401599999</v>
+        <v>-5.482993541199999</v>
       </c>
       <c r="Q98">
-        <v>-4.943053401599999</v>
+        <v>-5.028993541199999</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>1.21715091292901</v>
+        <v>1.60760121723868</v>
       </c>
       <c r="T98">
-        <v>10.03353858838018</v>
+        <v>13.37805145117357</v>
       </c>
       <c r="U98">
         <v>0.2358</v>
       </c>
       <c r="V98">
-        <v>0.103749540569748</v>
+        <v>0.1026799576772763</v>
       </c>
       <c r="W98">
-        <v>0.2113358583336535</v>
+        <v>0.2115880659796983</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9361,7 +9361,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.3458318018991599</v>
+        <v>0.3422665255909211</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9369,22 +9369,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.2534684605174677</v>
+        <v>0.2553684605174678</v>
       </c>
       <c r="C99">
-        <v>-34.52920647407443</v>
+        <v>-35.17804002861167</v>
       </c>
       <c r="D99">
-        <v>14.97481352592557</v>
+        <v>14.84663997138833</v>
       </c>
       <c r="E99">
-        <v>50.23802</v>
+        <v>50.75868</v>
       </c>
       <c r="F99">
-        <v>50.50402</v>
+        <v>51.02468</v>
       </c>
       <c r="G99">
         <v>1</v>
@@ -9405,37 +9405,37 @@
         <v>4.076000000000001</v>
       </c>
       <c r="M99">
-        <v>11.908847916</v>
+        <v>12.031619544</v>
       </c>
       <c r="N99">
-        <v>-7.832847915999999</v>
+        <v>-7.955619543999999</v>
       </c>
       <c r="O99">
-        <v>-2.3498543748</v>
+        <v>-2.3866858632</v>
       </c>
       <c r="P99">
-        <v>-5.482993541199999</v>
+        <v>-5.568933680799999</v>
       </c>
       <c r="Q99">
-        <v>-5.028993541199999</v>
+        <v>-5.114933680799999</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.60760121723868</v>
+        <v>2.38850182585802</v>
       </c>
       <c r="T99">
-        <v>13.37805145117357</v>
+        <v>20.06707717676036</v>
       </c>
       <c r="U99">
         <v>0.2358</v>
       </c>
       <c r="V99">
-        <v>0.1026799576772763</v>
+        <v>0.1016322030071</v>
       </c>
       <c r="W99">
-        <v>0.2115880659796983</v>
+        <v>0.2118351265309258</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9443,7 +9443,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.3422665255909211</v>
+        <v>0.3387740100236667</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9451,22 +9451,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.2553684605174678</v>
+        <v>0.2572684605174678</v>
       </c>
       <c r="C100">
-        <v>-35.17804002861167</v>
+        <v>-35.82469805853313</v>
       </c>
       <c r="D100">
-        <v>14.84663997138833</v>
+        <v>14.72064194146687</v>
       </c>
       <c r="E100">
-        <v>50.75868</v>
+        <v>51.27934</v>
       </c>
       <c r="F100">
-        <v>51.02468</v>
+        <v>51.54534</v>
       </c>
       <c r="G100">
         <v>1</v>
@@ -9487,37 +9487,37 @@
         <v>4.076000000000001</v>
       </c>
       <c r="M100">
-        <v>12.031619544</v>
+        <v>12.154391172</v>
       </c>
       <c r="N100">
-        <v>-7.955619543999999</v>
+        <v>-8.078391172</v>
       </c>
       <c r="O100">
-        <v>-2.3866858632</v>
+        <v>-2.4235173516</v>
       </c>
       <c r="P100">
-        <v>-5.568933680799999</v>
+        <v>-5.654873820400001</v>
       </c>
       <c r="Q100">
-        <v>-5.114933680799999</v>
+        <v>-5.200873820400001</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>2.38850182585802</v>
+        <v>4.73120365171604</v>
       </c>
       <c r="T100">
-        <v>20.06707717676036</v>
+        <v>40.13415435352071</v>
       </c>
       <c r="U100">
         <v>0.2358</v>
       </c>
       <c r="V100">
-        <v>0.1016322030071</v>
+        <v>0.1006056150979374</v>
       </c>
       <c r="W100">
-        <v>0.2118351265309258</v>
+        <v>0.2120771959599064</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9525,91 +9525,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.3387740100236667</v>
+        <v>0.335352050326458</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.2572684605174678</v>
-      </c>
-      <c r="C101">
-        <v>-35.82469805853313</v>
-      </c>
-      <c r="D101">
-        <v>14.72064194146687</v>
-      </c>
-      <c r="E101">
-        <v>51.27934</v>
-      </c>
-      <c r="F101">
-        <v>51.54534</v>
-      </c>
-      <c r="G101">
-        <v>1</v>
-      </c>
-      <c r="H101">
-        <v>51.8</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>4.53</v>
-      </c>
-      <c r="K101">
-        <v>0.454</v>
-      </c>
-      <c r="L101">
-        <v>4.076000000000001</v>
-      </c>
-      <c r="M101">
-        <v>12.154391172</v>
-      </c>
-      <c r="N101">
-        <v>-8.078391172</v>
-      </c>
-      <c r="O101">
-        <v>-2.4235173516</v>
-      </c>
-      <c r="P101">
-        <v>-5.654873820400001</v>
-      </c>
-      <c r="Q101">
-        <v>-5.200873820400001</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>4.73120365171604</v>
-      </c>
-      <c r="T101">
-        <v>40.13415435352071</v>
-      </c>
-      <c r="U101">
-        <v>0.2358</v>
-      </c>
-      <c r="V101">
-        <v>0.1006056150979374</v>
-      </c>
-      <c r="W101">
-        <v>0.2120771959599064</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>D2/D</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.335352050326458</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
